--- a/formulario t-12/Formulario_T12_Overfore_v1.3.xlsx
+++ b/formulario t-12/Formulario_T12_Overfore_v1.3.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cómo completarlo (interno)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FORMULARIO T-12" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pendientes por grupo (interno)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidencia de verificación" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sin cobertura (interno)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Cómo completarlo (interno)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FORMULARIO T-12" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Pendientes por grupo (interno)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Evidencia de verificación" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sin cobertura (interno)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'FORMULARIO T-12'!$7:$7</definedName>
@@ -762,7 +762,7 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 4 y 17</t>
+          <t>Subdoc. 4.1 v4.2, ap. 1.3 y 5</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 3.3 y 6</t>
+          <t>Subdoc. 4.1 v4.2, ap. 4.2, 4.3 y 7</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 1.1</t>
+          <t>Subdoc. 4.1 v4.2, ap. 1.1</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 1.2 y 18</t>
+          <t>Subdoc. 4.1 v4.2, ap. 1.2 y 21</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 4 capa 4 y 10</t>
+          <t>Subdoc. 4.1 v4.2, ap. 5, capa 4</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 8.3 y 10</t>
+          <t>Subdoc. 4.1 v4.2, ap. 10.3 y 12.2</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 4 capa 5 y 10</t>
+          <t>Subdoc. 4.1 v4.2, ap. 5, capa 5</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 10</t>
+          <t>Subdoc. 4.1 v4.2, ap. 12.4</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 9.4 y 10</t>
+          <t>Subdoc. 4.1 v4.2, ap. 11.5</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 10 y 13.1</t>
+          <t>Subdoc. 4.1 v4.2, ap. 12.2</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 10.2</t>
+          <t>Subdoc. 4.1 v4.2, ap. 12.5</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 3, ap. 2 · Catálogo RF-ADM-006</t>
+          <t>Subdoc. 3, ap. 2 · Catálogo RF-ADM-006 — Subdoc. 4.1 v4.2, ap. 15.7</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 7</t>
+          <t>Subdoc. 4.1 v4.2, ap. 9</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 8.1, 10 y 13.8</t>
+          <t>Subdoc. 4.1 v4.2, ap. 10.1 y 15.6</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 11.4 y 13.8</t>
+          <t>Subdoc. 4.1 v4.2, ap. 13.1 y 13.3</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 13.8</t>
+          <t>Subdoc. 4.1 v4.2, ap. 15.6</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 3, ap. 1.3 y 2.3 (bloque «Operación desconectada y sincronización») · Catálogo RF-DES-001, RNF-DIS-001</t>
+          <t>Subdoc. 3, ap. 1.3 y 2.3 (bloque «Operación desconectada y sincronización») · Catálogo RF-DES-001, RNF-DIS-001 — Subdoc. 4.1 v4.2, ap. 11.2</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 9 y 9.1</t>
+          <t>Subdoc. 4.1 v4.2, ap. 11.1 y 11.3</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 9.3</t>
+          <t>Subdoc. 4.1 v4.2, ap. 11.4</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 4 capa 8 y 12.1</t>
+          <t>Subdoc. 4.1 v4.2, ap. 5 capa 8, y 14.1</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 13.6</t>
+          <t>Subdoc. 4.1 v4.2, ap. 15.4</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 13.7</t>
+          <t>Subdoc. 4.1 v4.2, ap. 15.5</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 4 capa 3 y 14.1 — la calidad de servicio se declara aquí; el estudio de cobertura del rajo con zonas de sombra y proyección a tres años es del Subdoc. 4.2</t>
+          <t>Subdoc. 4.1 v4.2, ap. 5 capa 3 y 12.6 — la calidad de servicio y la priorización de tráfico se declaran ahí; el estudio de cobertura del rajo, con zonas de sombra y proyección a tres años, es del Subdoc. 4.2.</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 13.5</t>
+          <t>Subdoc. 4.1 v4.2, ap. 15.3</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 13.3</t>
+          <t>Subdoc. 4.1 v4.2, ap. 15.1</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 13.5</t>
+          <t>Subdoc. 4.1 v4.2, ap. 15.3</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 4 capa 6 y ADR-08</t>
+          <t>Subdoc. 4.1 v4.2, ap. 5 capa 6, y ADR-08 del ap. 21</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>Catálogo RF-ANA-008 · Subdoc. 3, ap. 5, criterio n.º 11</t>
+          <t>Catálogo RF-ANA-008 · Subdoc. 3, ap. 5, criterio n.º 11 — Subdoc. 4.1 v4.2, ap. 14.1</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 4 capa 3 y 8.3</t>
+          <t>Subdoc. 4.1 v4.2, ap. 5 capa 3, y 10.3</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 8.3</t>
+          <t>Subdoc. 4.1 v4.2, ap. 10.3</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 4 capa 3 y 8.3</t>
+          <t>Subdoc. 4.1 v4.2, ap. 5 capa 3, y 10.3</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 8.3 y 12.1</t>
+          <t>Subdoc. 4.1 v4.2, ap. 10.3 y 14.1</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 8.1</t>
+          <t>Subdoc. 4.1 v4.2, ap. 10.1</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 4 capa 6</t>
+          <t>Subdoc. 4.1 v4.2, ap. 5, capa 6</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 11.9</t>
+          <t>Subdoc. 4.1 v4.2, ap. 13.8</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="E157" s="9" t="inlineStr">
         <is>
-          <t>Catálogo RNF-CAP-001, RNF-CAP-006 · Registro de supuestos SUP-31</t>
+          <t>Catálogo RNF-CAP-001, RNF-CAP-006 · Registro de supuestos SUP-31 — Subdoc. 4.1 v4.2, ap. 12.1 y 12.6</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="E158" s="9" t="inlineStr">
         <is>
-          <t>Catálogo RNF-CAP-001, RNF-CAP-006, RNF-DES-001 a RNF-DES-006</t>
+          <t>Catálogo RNF-CAP-001, RNF-CAP-006, RNF-DES-001 a RNF-DES-006 — Subdoc. 4.1 v4.2, ap. 12.1</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="E159" s="9" t="inlineStr">
         <is>
-          <t>Catálogo RNF-CAP-014</t>
+          <t>Catálogo RNF-CAP-014 — Subdoc. 4.1 v4.2, ap. 12.6</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="E160" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 10 y 13.1</t>
+          <t>Subdoc. 4.1 v4.2, ap. 12.2</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="E161" s="9" t="inlineStr">
         <is>
-          <t>Catálogo RNF-ESC-002</t>
+          <t>Catálogo RNF-ESC-002 — Subdoc. 4.1 v4.2, ap. 12.6</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="E164" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 13.2</t>
+          <t>Subdoc. 4.1 v4.2, ap. 12.3</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="E176" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 11.1</t>
+          <t>Subdoc. 4.1 v4.2, ap. 13.1</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="E177" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 11.2</t>
+          <t>Subdoc. 4.1 v4.2, ap. 13.5</t>
         </is>
       </c>
     </row>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="E178" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 11.3</t>
+          <t>Subdoc. 4.1 v4.2, ap. 13.2</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="E182" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 11.4</t>
+          <t>Subdoc. 4.1 v4.2, ap. 13.3</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="E183" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 11.5</t>
+          <t>Subdoc. 4.1 v4.2, ap. 13.4</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="E184" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 11.5</t>
+          <t>Subdoc. 4.1 v4.2, ap. 13.4</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="E185" s="9" t="inlineStr">
         <is>
-          <t>Catálogo RF-SSO-007, RF-SSO-010 · Registro de supuestos SUP-25</t>
+          <t>Catálogo RF-SSO-007, RF-SSO-010 · Registro de supuestos SUP-25 — Subdoc. 4.1 v4.2, ap. 13.2 y 13.4</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="E186" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 11.6</t>
+          <t>Subdoc. 4.1 v4.2, ap. 5, capa 3</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="E187" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 11.4</t>
+          <t>Subdoc. 4.1 v4.2, ap. 13.3</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="E188" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 11.4, con la enumeración concreta en el Subdoc. 4.2</t>
+          <t>Subdoc. 4.1 v4.2, ap. 13.3. La enumeracion concreta de dominios, puertos y servicios es del Subdoc. 4.2.</t>
         </is>
       </c>
     </row>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="E189" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 11.7</t>
+          <t>Subdoc. 4.1 v4.2, ap. 14.5</t>
         </is>
       </c>
     </row>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="E190" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 11.7</t>
+          <t>Subdoc. 4.1 v4.2, ap. 13.6</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="E200" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 11.8</t>
+          <t>Subdoc. 4.1 v4.2, ap. 13.7</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="E202" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 11.8</t>
+          <t>Subdoc. 4.1 v4.2, ap. 13.7</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="E205" s="9" t="inlineStr">
         <is>
-          <t>Catálogo de requerimientos v2.4 · RF-IDE-021</t>
+          <t>Catálogo de requerimientos v2.4 · RF-IDE-021 — Subdoc. 4.1 v4.2, ap. 5, capa 7</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="E206" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 4 capa 7 y 11.9</t>
+          <t>Subdoc. 4.1 v4.2, ap. 5 capa 7, y 13.8</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="E207" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 11.9</t>
+          <t>Subdoc. 4.1 v4.2, ap. 13.8</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="E210" s="9" t="inlineStr">
         <is>
-          <t>Catálogo de requerimientos v2.4 · RF-IDE-023, RF-IDE-019</t>
+          <t>Catálogo de requerimientos v2.4 · RF-IDE-023, RF-IDE-019 — Subdoc. 4.1 v4.2, ap. 13.1</t>
         </is>
       </c>
     </row>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="E214" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 3, ap. 2.3 (bloque de identidad) · Catálogo RF-IDE-002, RF-IDE-003, RNF-DES-005 · Registro de supuestos SUP-04 y SUP-29</t>
+          <t>Subdoc. 3, ap. 2.3 (bloque de identidad) · Catálogo RF-IDE-002, RF-IDE-003, RNF-DES-005 · Registro de supuestos SUP-04 y SUP-29 — Subdoc. 4.1 v4.2, ap. 5, capa 7</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="E215" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 3, ap. 2.3 y 5, criterio n.º 8 · Catálogo RF-IDE-005, RF-IDE-009 · Registro de supuestos SUP-08</t>
+          <t>Subdoc. 3, ap. 2.3 y 5, criterio n.º 8 · Catálogo RF-IDE-005, RF-IDE-009 · Registro de supuestos SUP-08 — Subdoc. 4.1 v4.2, ap. 5, capa 7</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="E217" s="9" t="inlineStr">
         <is>
-          <t>Catálogo de requerimientos v2.4 · RNF-USA-007</t>
+          <t>Catálogo de requerimientos v2.4 · RNF-USA-007 — Subdoc. 4.1 v4.2, ap. 16.5</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="E224" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 3, ap. 5, criterio n.º 14 · Catálogo RNF-USA-001, RNF-USA-002, RNF-USA-003</t>
+          <t>Subdoc. 3, ap. 5, criterio n.º 14 · Catálogo RNF-USA-001, RNF-USA-002, RNF-USA-003 — Subdoc. 4.1 v4.2, ap. 16.8</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="E227" s="9" t="inlineStr">
         <is>
-          <t>Catálogo de requerimientos v2.4 · RNF-USA-013</t>
+          <t>Catálogo de requerimientos v2.4 · RNF-USA-013 — Subdoc. 4.1 v4.2, ap. 16.5</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="E228" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 16.5</t>
+          <t>Subdoc. 4.1 v4.2, ap. 16.5</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="E229" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 4 capa 8 y 12.1</t>
+          <t>Subdoc. 4.1 v4.2, ap. 5 capa 8, y 14.1</t>
         </is>
       </c>
     </row>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="E230" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 12.5</t>
+          <t>Subdoc. 4.1 v4.2, ap. 14.5</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="E231" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 12.2</t>
+          <t>Subdoc. 4.1 v4.2, ap. 14.2</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="E232" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 12.3</t>
+          <t>Subdoc. 4.1 v4.2, ap. 14.3</t>
         </is>
       </c>
     </row>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="E235" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 12.4</t>
+          <t>Subdoc. 4.1 v4.2, ap. 14.4</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="E236" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 12.6</t>
+          <t>Subdoc. 4.1 v4.2, ap. 14.5</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="E237" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 12.7</t>
+          <t>Subdoc. 4.1 v4.2, ap. 14.6</t>
         </is>
       </c>
     </row>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="E239" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 16.6</t>
+          <t>Subdoc. 4.1 v4.2, ap. 15.8</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="E248" s="9" t="inlineStr">
         <is>
-          <t>Catálogo RF-ADM-002, RF-ADM-003, RF-ADM-004 · Registro de reglas de negocio (numeral 17.1)</t>
+          <t>Catálogo RF-ADM-002, RF-ADM-003, RF-ADM-004 · Registro de reglas de negocio (numeral 17.1) — Subdoc. 4.1 v4.2, ap. 15.1</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="E249" s="9" t="inlineStr">
         <is>
-          <t>Catálogo de requerimientos v2.4 · RF-ADM-013, RF-ADM-002, RF-ADM-004</t>
+          <t>Catálogo de requerimientos v2.4 · RF-ADM-013, RF-ADM-002, RF-ADM-004 — Subdoc. 4.1 v4.2, ap. 15.1</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="E251" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 13.4</t>
+          <t>Subdoc. 4.1 v4.2, ap. 15.2</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="E256" s="9" t="inlineStr">
         <is>
-          <t>Catálogo RF-ADM-009 · Cap. 15 del caso (RT-05.10)</t>
+          <t>Catálogo RF-ADM-009 · Cap. 15 del caso (RT-05.10) — Subdoc. 4.1 v4.2, ap. 14.5</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="E261" s="9" t="inlineStr">
         <is>
-          <t>Catálogo de requerimientos v2.4 · RF-ADM-017, RF-IDE-005, RF-AMB-004</t>
+          <t>Catálogo de requerimientos v2.4 · RF-ADM-017, RF-IDE-005, RF-AMB-004 — Subdoc. 4.1 v4.2, ap. 5, capa 6</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="E272" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 16.7</t>
+          <t>Subdoc. 4.1 v4.2, ap. 16.6</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="E273" s="9" t="inlineStr">
         <is>
-          <t>Catálogo de requerimientos v2.4 · RF-ANA-010, RF-IDE-018</t>
+          <t>Catálogo de requerimientos v2.4 · RF-ANA-010, RF-IDE-018 — Subdoc. 4.1 v4.2, ap. 16.9</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="E275" s="9" t="inlineStr">
         <is>
-          <t>Catálogo de requerimientos v2.4 · RF-ANA-011, RF-ADM-001</t>
+          <t>Catálogo de requerimientos v2.4 · RF-ANA-011, RF-ADM-001 — Subdoc. 4.1 v4.2, ap. 12.3</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="E282" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 16.2 y 16.3</t>
+          <t>Subdoc. 4.1 v4.2, ap. 16.2 y 16.3</t>
         </is>
       </c>
     </row>
@@ -6507,7 +6507,7 @@
       </c>
       <c r="E283" s="9" t="inlineStr">
         <is>
-          <t>Catálogo de requerimientos v2.4 · RNF-POR-004, RF-ADM-011</t>
+          <t>Catálogo de requerimientos v2.4 · RNF-POR-004, RF-ADM-011 — Subdoc. 4.1 v4.2, ap. 16.1</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="E287" s="9" t="inlineStr">
         <is>
-          <t>Catálogo de requerimientos v2.4 · RNF-DES-014, RNF-USA-003</t>
+          <t>Catálogo de requerimientos v2.4 · RNF-DES-014, RNF-USA-003 — Subdoc. 4.1 v4.2, ap. 16.7</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="E288" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 v3.0, ap. 16.4</t>
+          <t>Subdoc. 4.1 v4.2, ap. 16.4</t>
         </is>
       </c>
     </row>

--- a/formulario t-12/Formulario_T12_Overfore_v1.3.xlsx
+++ b/formulario t-12/Formulario_T12_Overfore_v1.3.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cómo completarlo (interno)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="FORMULARIO T-12" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Pendientes por grupo (interno)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Evidencia de verificación" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sin cobertura (interno)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cómo completarlo (interno)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FORMULARIO T-12" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pendientes por grupo (interno)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidencia de verificación" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sin cobertura (interno)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'FORMULARIO T-12'!$7:$7</definedName>
@@ -704,7 +704,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
@@ -6099,7 +6098,7 @@
       </c>
       <c r="E267" s="9" t="inlineStr">
         <is>
-          <t>Catálogo RF-ADM-002, RF-MTO-005</t>
+          <t>Subdoc. 4.1 v4.2, ap. 16.6</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8080,6 @@
       <c r="D381" s="9" t="inlineStr"/>
       <c r="E381" s="9" t="inlineStr"/>
     </row>
-    <row r="382"/>
     <row r="383" ht="22" customHeight="1">
       <c r="A383" s="6" t="inlineStr">
         <is>

--- a/formulario t-12/Formulario_T12_Overfore_v1.3.xlsx
+++ b/formulario t-12/Formulario_T12_Overfore_v1.3.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -651,6 +651,18 @@
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>1) El Subdocumento 4.1 v3.0 se entrega y acredita 61 requisitos transversales que estaban en blanco: el Capítulo 2 completo salvo RT-02.12, que ya estaba declarado, más RT-03.04, 03.07, 03.11, 03.16, 03.18, 03.19; RT-04.07, 04.08, 04.10; RT-05.05, 05.16, 05.17, 05.18, 05.19, 05.23, 05.29; RT-06.20; RT-09.04, 09.08; RT-11.01, 11.02, 11.03, 11.07, 11.08, 11.09, 11.11, 11.12, 11.13, 11.14, 11.15, 11.25, 11.27; RT-12.03, 12.04; RT-13.12; RT-14.01, 14.02, 14.03, 14.04, 14.07, 14.08, 14.09; RT-15.02; RT-16.05, 16.26; RT-17.02, 17.08. 2) RT-03.13 pasa de «Cumple parcialmente» a «Cumple»: el apartado 9.3 del 4.1 entrega la lista de funciones degradadas. 3) RT-03.24 queda parcialmente acreditado: la calidad de servicio está en el 4.1; el estudio de cobertura del rajo es del 4.2. 4) De los 97 códigos que la v1.2 asignaba a «Subdoc. 4.1», 52 quedan cerrados por ese entregable y 45 se reasignan con fundamento en su apartado 15, porque no son materia de arquitectura lógica. 5) Se agregan 55 filas a la hoja «Evidencia de verificación».</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Revisión de consistencia · v1.3.1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4 de septiembre de 2026. 1) Se declaran los 89 requisitos transversales que acreditan los entregables emitidos después de la v1.3: Subdocumento 4.2 v1.1 y Formulario T-11 v1.0 (66), Subdocumento 5 v2.1 (19) y Subdocumento 1 v1.0 (4, como cumplimiento parcial, porque el sitio corporativo es simulado). 2) La hoja «Pendientes por grupo» se reapunta del Subdocumento 4.1 v3.0 a la v4.2, cuya renumeración de apartados dejó obsoletas las remisiones anteriores, y el reparto de códigos se cita contra su apartado 19. 3) Quedan en blanco, a propósito, los requisitos cuyos entregables aún no existen: Subdocumentos 6, 7, 9, 10, 11, 12 y 13, prototipo interactivo, video de presentación y Oferta Económica. Una fila en blanco es honesta; una fila con «Cumple» sin componente ni sección, no.</t>
         </is>
       </c>
     </row>
@@ -700,7 +712,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Proponente: OVERFORE S.A.   ·   Licitación TFEP-01/2026 — Caso 01 · Minería   ·   Formulario T-12 v1.3 — 1 de septiembre de 2026</t>
+          <t>Proponente: OVERFORE S.A.   ·   Licitación TFEP-01/2026 — Caso 01 · Minería   ·   Formulario T-12 v1.3.1 — 4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -1127,9 +1139,21 @@
           <t>El PROPONENTE declarará el proveedor de nube pública, la región primaria y la región secundaria utilizadas. El proveedor deberá contar con presencia de región o zona en Chile o en Sudamérica.</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr"/>
-      <c r="D22" s="9" t="inlineStr"/>
-      <c r="E22" s="9" t="inlineStr"/>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base: Azure Chile Central primaria y Brazil South secundaria</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 1 y 3 · T-11 ítems T11-01 y T11-02</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -1142,9 +1166,21 @@
           <t>Todos los componentes con requisito de alta disponibilidad se desplegarán en al menos dos zonas de disponibilidad. No se aceptará un diseño en una sola zona.</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr"/>
-      <c r="D23" s="9" t="inlineStr"/>
-      <c r="E23" s="9" t="inlineStr"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base; los componentes centrales C-01, C-02, C-05, C-08, C-15, C-16, C-19 y C-20</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 3 y 13 · T-11 ítems T11-03 y T11-05</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -1157,9 +1193,21 @@
           <t>La totalidad de la infraestructura se definirá como código, versionada en el repositorio del CLIENTE, revisable y reproducible. No se admite infraestructura creada manualmente por consola, salvo la cuenta raíz inicial, cuya creación deberá documentarse.</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr"/>
-      <c r="D24" s="9" t="inlineStr"/>
-      <c r="E24" s="9" t="inlineStr"/>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (Terraform/OpenTofu sobre el repositorio Git del CLIENTE)</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 6 · T-11 ítem T11-14</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -1199,9 +1247,21 @@
           <t>El PROPONENTE privilegiará servicios administrados por sobre servicios autoadministrados cuando ello reduzca el riesgo operacional, y justificará cada excepción.</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr"/>
-      <c r="D26" s="9" t="inlineStr"/>
-      <c r="E26" s="9" t="inlineStr"/>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base; servicios administrados de persistencia, claves y analítica</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 6 · T-11 ítems T11-03 a T11-13</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -1214,9 +1274,21 @@
           <t>Se aplicarán prácticas FinOps: etiquetado obligatorio de todos los recursos por ambiente, módulo y centro de costo; presupuestos con alertas de desviación; y reporte mensual de consumo desglosado entregado al CLIENTE.</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr"/>
-      <c r="D27" s="9" t="inlineStr"/>
-      <c r="E27" s="9" t="inlineStr"/>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Cumple parcialmente</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (etiquetado FinOps y Azure Policy en la Landing Zone)</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 6 · T-11 ítem T11-01. PENDIENTE: los presupuestos con alerta de desviación y el reporte mensual de consumo desglosado se cierran en la Oferta Económica</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -1271,9 +1343,21 @@
           <t>Se valorará el uso de cómputo sin servidor o de contenedores administrados para las cargas de perfil variable, con el análisis comparativo de costo frente a instancias permanentes.</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr"/>
-      <c r="D30" s="9" t="inlineStr"/>
-      <c r="E30" s="9" t="inlineStr"/>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Cumple parcialmente</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (AKS administrado; clúster no productivo escalable a cero fuera de uso)</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 6 · T-11 ítem T11-03. PENDIENTE: el análisis comparativo de costo frente a instancias permanentes se presenta en la Oferta Económica</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -1394,9 +1478,21 @@
           <t>Los equipos on-premise críticos serán redundantes. El almacenamiento local tolerará la falla de al menos un disco; el PROPONENTE declarará el nivel RAID escogido y lo justificará frente a las alternativas.</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr"/>
-      <c r="D35" s="9" t="inlineStr"/>
-      <c r="E35" s="9" t="inlineStr"/>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base on-premise: clúster N+1 con RAID1 local y arreglos RAID6 de doble controladora con hot spare</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7, 8 y 13 · T-11 ítems T11-15 a T11-19</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -1409,9 +1505,21 @@
           <t>Los sistemas on-premise se endurecerán conforme a los CIS Benchmarks aplicables, con gestión centralizada de parches y ventana de aplicación acordada con el CLIENTE.</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr"/>
-      <c r="D36" s="9" t="inlineStr"/>
-      <c r="E36" s="9" t="inlineStr"/>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (CIS Benchmarks, firmware firmado, Secure Boot/TPM y parches centralizados)</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 14</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -1451,9 +1559,21 @@
           <t>El enlace entre el sitio on-premise y la nube será redundante, con caminos físicos y proveedores distintos, y conmutación automática con tiempo de conmutación declarado.</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr"/>
-      <c r="D38" s="9" t="inlineStr"/>
-      <c r="E38" s="9" t="inlineStr"/>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Cumple parcialmente</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base: dos carriers, dos routers de borde por sitio y conmutación WAN automática</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 4, 7 y 12 · T-11 ítems T11-22 a T11-24. PENDIENTE: el tiempo de conmutación se declara al cerrar VAL-06, que verifica ductos y puntos de entrada físicamente distintos</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -1520,9 +1640,21 @@
           <t>El PROPONENTE dimensionará el ancho de banda requerido por sitio, en régimen normal y en peak, y lo justificará con el cálculo de volumen de transacciones y de datos.</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr"/>
-      <c r="D41" s="9" t="inlineStr"/>
-      <c r="E41" s="9" t="inlineStr"/>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (20 Mbps en régimen y 50 en peak en faena; 2 a 5 Mbps en sitios remotos)</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 12 · Subdoc. 5 v2.1, ap. 4.6</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -1535,9 +1667,21 @@
           <t>La conexión entre la red del CLIENTE y la nube se establecerá mediante enlace privado dedicado o red privada virtual con cifrado, según lo que el volumen y la criticidad justifiquen.</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr"/>
-      <c r="D42" s="9" t="inlineStr"/>
-      <c r="E42" s="9" t="inlineStr"/>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (enlace privado o red privada virtual cifrada; zona Z2, puerta operacional)</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 4 y 12 · Matriz de Distribución v1.0, hoja «Flujos físicos»</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -1550,9 +1694,21 @@
           <t>El acceso remoto de las personas trabajadoras del CLIENTE, incluido el trabajo desde el hogar, se resolverá con acceso a la red de confianza cero, con verificación de postura del dispositivo. No se admite exponer servicios internos directamente a Internet.</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr"/>
-      <c r="D43" s="9" t="inlineStr"/>
-      <c r="E43" s="9" t="inlineStr"/>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (Zero Trust con verificación de postura del dispositivo; zona Z5 de gestión)</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 4 y 14</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -1865,9 +2021,21 @@
           <t>El PROPONENTE entregará el modelo de datos documentado y un diccionario de datos con el nombre, el tipo, el dominio de valores, la obligatoriedad, el propietario y la sensibilidad de cada atributo.</t>
         </is>
       </c>
-      <c r="C60" s="9" t="inlineStr"/>
-      <c r="D60" s="9" t="inlineStr"/>
-      <c r="E60" s="9" t="inlineStr"/>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>Las 42 entidades del modelo, sobre C-01, C-05, C-15, C-17, C-18 y C-20</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 5 v2.1, ap. 1.2 y 1.6 · anexo Diccionario_Datos v2.1, hojas «Diccionario» y «Entidades»</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
@@ -1880,9 +2048,21 @@
           <t>El PROPONENTE justificará la selección del paradigma y del motor de persistencia: relacional o no relacional, garantías transaccionales, y la posición escogida entre consistencia y disponibil idad conforme al teorema CAP, para cada dominio de datos.</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr"/>
-      <c r="D61" s="9" t="inlineStr"/>
-      <c r="E61" s="9" t="inlineStr"/>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>Las seis naturalezas de persistencia de C-22 — Plataforma base</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 5 v2.1, ap. 2.1 a 2.4 · anexo Diccionario_Datos v2.1, hoja «Dominios»</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
@@ -1895,9 +2075,21 @@
           <t>Toda operación de negocio será trazable: la solución permitirá reconstruir quién, qué, cuándo, desde qué dispositivo y con qué valores anteriores y posteriores, para cualquier registro y en cualquier momento del período de retención.</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr"/>
-      <c r="D62" s="9" t="inlineStr"/>
-      <c r="E62" s="9" t="inlineStr"/>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>C-20 — Administración, parametrización y auditoría (asiento de auditoría inalterable)</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 5 v2.1, ap. 2.3 y 6.5 · anexo Diccionario_Datos v2.1, entidad Asiento de auditoría</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
@@ -1910,9 +2102,21 @@
           <t>La calidad de datos se gestionará conforme a ISO/IEC 25012, con validación en el punto de captura, indicadores de completitud, exactitud y consistencia, y tablero de calidad disponible para el CLIENTE.</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr"/>
-      <c r="D63" s="9" t="inlineStr"/>
-      <c r="E63" s="9" t="inlineStr"/>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>C-19 — Analítica, indicadores y reportería (tablero de calidad de datos)</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 5 v2.1, ap. 6.1</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
@@ -1952,9 +2156,21 @@
           <t>La solución permitirá exportar la totalidad de la información del CLIENTE en formatos abiertos y documentados, en cualquier momento del Contrato, sin costo adicional y sin intervención del ADJUDICATARIO.</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr"/>
-      <c r="D65" s="9" t="inlineStr"/>
-      <c r="E65" s="9" t="inlineStr"/>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>C-19 — Analítica, indicadores y reportería; C-20 — Administración, parametrización y auditoría</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 5 v2.1, ap. 5.4 y 6.4</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
@@ -1994,9 +2210,21 @@
           <t>Los datos personales se tratarán conforme al Artículo 85.º de las Bases Administrativas, con seudonimización o cifrado a nivel de campo para las categorías sensibles que el caso identifique.</t>
         </is>
       </c>
-      <c r="C67" s="9" t="inlineStr"/>
-      <c r="D67" s="9" t="inlineStr"/>
-      <c r="E67" s="9" t="inlineStr"/>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>C-05 — Identidad y acreditación; C-18 — Seguridad y salud ocupacional</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 5 v2.1, ap. 1.3 y 6.5</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
@@ -2009,9 +2237,21 @@
           <t>El PROPONENTE presentará una estrategia de gestión de datos maestros que evite la duplicación de entidades compartidas entre módulos y con sistemas externos.</t>
         </is>
       </c>
-      <c r="C68" s="9" t="inlineStr"/>
-      <c r="D68" s="9" t="inlineStr"/>
-      <c r="E68" s="9" t="inlineStr"/>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>Los seis maestros compartidos con C-06, C-09, C-10, C-11, C-12 y C-20</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 5 v2.1, ap. 1.4</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
@@ -2078,9 +2318,21 @@
           <t>La migración incluirá una etapa de perfilado y saneamiento previo, con informe de los defectos detectados en los datos de origen y la decisión adoptada sobre cada uno.</t>
         </is>
       </c>
-      <c r="C71" s="9" t="inlineStr"/>
-      <c r="D71" s="9" t="inlineStr"/>
-      <c r="E71" s="9" t="inlineStr"/>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>C-21 — Migración de datos históricos</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 5 v2.1, ap. 3.2, fases 1 y 2</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
@@ -2093,9 +2345,21 @@
           <t>Se ejecutarán al menos dos ensayos completos de migración sobre Preproducción antes de la migración definitiva, con medición del tiempo total y del resultado de la conciliación.</t>
         </is>
       </c>
-      <c r="C72" s="9" t="inlineStr"/>
-      <c r="D72" s="9" t="inlineStr"/>
-      <c r="E72" s="9" t="inlineStr"/>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>C-21 — Migración de datos históricos</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 5 v2.1, ap. 3.2, fase 3, y ap. 3.3</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
@@ -2108,9 +2372,21 @@
           <t>La conciliación posterior a la migración será cuantitativa y verificable: recuentos, sumas de control y muestreo dirigido. Toda diferencia deberá quedar explicada.</t>
         </is>
       </c>
-      <c r="C73" s="9" t="inlineStr"/>
-      <c r="D73" s="9" t="inlineStr"/>
-      <c r="E73" s="9" t="inlineStr"/>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>C-21 — Migración de datos históricos</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 5 v2.1, ap. 3.2, fase 5, y ap. 3.3</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
@@ -2258,9 +2534,21 @@
           <t>Las integraciones con sistemas heredados o de terceros se aislarán mediante una capa anti corrupción, de modo que un cambio en el sistema externo no propague su modelo al núcleo de la solución.</t>
         </is>
       </c>
-      <c r="C79" s="9" t="inlineStr"/>
-      <c r="D79" s="9" t="inlineStr"/>
-      <c r="E79" s="9" t="inlineStr"/>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>Los siete adaptadores C-09 a C-14 y el adaptador de control de fatiga</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 5 v2.1, ap. 1.5</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
@@ -2273,9 +2561,21 @@
           <t>El PROPONENTE declarará, por cada integración, el modo (síncrono o asíncrono), el volumen esperado, la ventana de disponibilidad del sistema contraparte y el comportamiento de la solución cuando ese sistema no responde.</t>
         </is>
       </c>
-      <c r="C80" s="9" t="inlineStr"/>
-      <c r="D80" s="9" t="inlineStr"/>
-      <c r="E80" s="9" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>Cumple parcialmente</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>Los siete adaptadores C-09 a C-14 y el adaptador de control de fatiga</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 5 v2.1, ap. 1.5 y 4.5. PENDIENTE: la ventana de disponibilidad de cada sistema contraparte se cierra con la Consulta N.º 5 y con el levantamiento VAL-03 del Subdoc. 4.2</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
@@ -2288,9 +2588,21 @@
           <t>La solución soportará la carga y descarga masiva de información en formatos abiertos, con va lidación previa, informe de errores por registro y procesamiento parcial.</t>
         </is>
       </c>
-      <c r="C81" s="9" t="inlineStr"/>
-      <c r="D81" s="9" t="inlineStr"/>
-      <c r="E81" s="9" t="inlineStr"/>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>Cumple parcialmente</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>C-06 — Portal de empresas contratistas; C-21 — Migración de datos históricos</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 5 v2.1, ap. 3.2, fase 4, con cuarentena por registro y motivo de lista cerrada. PENDIENTE: la carga y descarga masiva como función de operación se desarrolla con la familia RF-ADM del catálogo</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
@@ -2345,9 +2657,21 @@
           <t>La solución proveerá una capa analítica con tableros operacionales y de gestión, construidos sobre los indicadores que las Bases Técnicas del caso definan.</t>
         </is>
       </c>
-      <c r="C84" s="9" t="inlineStr"/>
-      <c r="D84" s="9" t="inlineStr"/>
-      <c r="E84" s="9" t="inlineStr"/>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>C-19 — Analítica, indicadores y reportería</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 5 v2.1, ap. 5.1 y 5.4</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
@@ -2360,9 +2684,21 @@
           <t>Los tableros permitirán filtrar por período, unidad organizacional y dimensiones propias del caso, y profundizar desde el indicador agregado hasta la transacción de origen.</t>
         </is>
       </c>
-      <c r="C85" s="9" t="inlineStr"/>
-      <c r="D85" s="9" t="inlineStr"/>
-      <c r="E85" s="9" t="inlineStr"/>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>C-19 — Analítica, indicadores y reportería</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 5 v2.1, ap. 5.2 y 5.3</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
@@ -2375,9 +2711,21 @@
           <t>El CLIENTE podrá construir sus propios informes sin intervención del ADJUDICATARIO, mediante una herramienta de autoservicio con modelo semántico documentado.</t>
         </is>
       </c>
-      <c r="C86" s="9" t="inlineStr"/>
-      <c r="D86" s="9" t="inlineStr"/>
-      <c r="E86" s="9" t="inlineStr"/>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>C-19 — Analítica, indicadores y reportería (consulta autoservida sobre el modelo dimensional)</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 5 v2.1, ap. 5.3 y 5.4</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
@@ -2390,9 +2738,21 @@
           <t>Todo informe será exportable en formatos abiertos y programable para envío automático por calendario.</t>
         </is>
       </c>
-      <c r="C87" s="9" t="inlineStr"/>
-      <c r="D87" s="9" t="inlineStr"/>
-      <c r="E87" s="9" t="inlineStr"/>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>Cumple parcialmente</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>C-19 — Analítica, indicadores y reportería</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 5 v2.1, ap. 5.4. PENDIENTE: la programación de envío por calendario se desarrolla con la familia RF-ANA del catálogo</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
@@ -2447,11 +2807,19 @@
           <t>El espacio asignado será de uso exclus ivo de la solución y estará aislado de otras dependencias del CLIENTE, con acceso independiente.</t>
         </is>
       </c>
-      <c r="C90" s="9" t="inlineStr"/>
-      <c r="D90" s="9" t="inlineStr"/>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base: recinto técnico exclusivo de faena y sala del CIO, con acceso independiente</t>
+        </is>
+      </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.2 — Arquitectura física (Grupo 3)</t>
+          <t>Subdoc. 4.2 v1.1, ap. 7 y 8</t>
         </is>
       </c>
     </row>
@@ -2481,9 +2849,21 @@
           <t>El PROPONENTE entregará el plano de distribución interna del recinto, con la separación de las zonas de generadores, baterías, climatización, servidores, comunicaciones, trabajo y respaldo.</t>
         </is>
       </c>
-      <c r="C92" s="9" t="inlineStr"/>
-      <c r="D92" s="9" t="inlineStr"/>
-      <c r="E92" s="9" t="inlineStr"/>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>Cumple parcialmente</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (distribución de racks y zonas de energía, clima, servidores, comunicaciones, trabajo y respaldo)</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7 y Anexo A, lámina B. PENDIENTE: el plano de distribución interna se emite tras el levantamiento VAL-01</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
@@ -2511,9 +2891,21 @@
           <t>Los racks de servidores serán independientes de los racks de equipos de comunicación. Se declarará la ocupación proyectada de cada rack y su margen de crecimiento.</t>
         </is>
       </c>
-      <c r="C94" s="9" t="inlineStr"/>
-      <c r="D94" s="9" t="inlineStr"/>
-      <c r="E94" s="9" t="inlineStr"/>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (2 racks de servidores y datos, 1 de comunicaciones, ≥30 % de U y puertos libres)</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7 y 8 · T-11 ítems T11-25 y T11-26</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
@@ -2526,9 +2918,21 @@
           <t>La obra civil de separación de las instalaciones es de cargo del CLIENTE; su 1 especificación técnica y su coordinación son de cargo del PROPONENTE.</t>
         </is>
       </c>
-      <c r="C95" s="9" t="inlineStr"/>
-      <c r="D95" s="9" t="inlineStr"/>
-      <c r="E95" s="9" t="inlineStr"/>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>No aplica: reparto de responsabilidad. Obra civil de cargo del CLIENTE; especificación técnica y coordinación del PROPONENTE</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7 y 15</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
@@ -2541,9 +2945,21 @@
           <t>El suministro eléctrico de los equipos será ininterrumpido, con sistema de alimentación ininterrumpida dimensionado para una autonomía mínima de 30 minutos a plena carga.</t>
         </is>
       </c>
-      <c r="C96" s="9" t="inlineStr"/>
-      <c r="D96" s="9" t="inlineStr"/>
-      <c r="E96" s="9" t="inlineStr"/>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (UPS modular N+1, ≥15 kVA, ≥30 min a plena carga, con bypass de mantenimiento)</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7 · T-11 ítem T11-27</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
@@ -2556,9 +2972,21 @@
           <t>La capacidad de generación autónoma asegurará un rango mínimo de 24 horas continuas de operación, con estanque de combustible dimensionado y contrato de reabastecimiento declarado.</t>
         </is>
       </c>
-      <c r="C97" s="9" t="inlineStr"/>
-      <c r="D97" s="9" t="inlineStr"/>
-      <c r="E97" s="9" t="inlineStr"/>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (generador ≥24 h con ATS, estanque dimensionado y contrato de reabastecimiento)</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7 · T-11 ítem T11-28</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
@@ -2601,9 +3029,21 @@
           <t>El PROPONENTE declarará la carga eléctrica proyectada en kW, el factor de potencia y la eficiencia en el uso de la energía (PUE) estimada del recinto.</t>
         </is>
       </c>
-      <c r="C100" s="9" t="inlineStr"/>
-      <c r="D100" s="9" t="inlineStr"/>
-      <c r="E100" s="9" t="inlineStr"/>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base: carga TI de diseño 6,0 kW, factor de potencia ≥0,95, PUE objetivo ≤1,55, demanda total ≤9,3 kW</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
@@ -2616,9 +3056,21 @@
           <t>Se valorará la redundancia de alimentación en configuración 2N o N+1 con doble acometida y transferencia automática.</t>
         </is>
       </c>
-      <c r="C101" s="9" t="inlineStr"/>
-      <c r="D101" s="9" t="inlineStr"/>
-      <c r="E101" s="9" t="inlineStr"/>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>Cumple parcialmente</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (UPS N+1, ATS y bandas PDU A/B)</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7 y Anexo A, lámina B · T-11 ítems T11-27 y T11-28. PENDIENTE: la doble acometida depende del levantamiento eléctrico VAL-01</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
@@ -2631,9 +3083,21 @@
           <t>El recinto contará con climatización de precisión para operación continua, redundante en configuración N+1, con control de temperatura y de humedad relativa dentro de los rangos que recomienda el fabricante del equipamiento.</t>
         </is>
       </c>
-      <c r="C102" s="9" t="inlineStr"/>
-      <c r="D102" s="9" t="inlineStr"/>
-      <c r="E102" s="9" t="inlineStr"/>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (climatización de precisión N+1 con control de temperatura y humedad relativa)</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7 · T-11 ítem T11-29</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
@@ -2646,9 +3110,21 @@
           <t>Se monitorearán en línea la temperatura, la humedad y la presencia de agua, con alertamiento integrado a la plataforma de observabilidad.</t>
         </is>
       </c>
-      <c r="C103" s="9" t="inlineStr"/>
-      <c r="D103" s="9" t="inlineStr"/>
-      <c r="E103" s="9" t="inlineStr"/>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (temperatura, humedad y fuga de agua integradas a la observabilidad de C-22)</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7 · T-11 ítems T11-29 y T11-13</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
@@ -2661,9 +3137,21 @@
           <t>El PROPONENTE declarará la estrategia de contención de pasillo frío o caliente y su efecto en la eficiencia energética.</t>
         </is>
       </c>
-      <c r="C104" s="9" t="inlineStr"/>
-      <c r="D104" s="9" t="inlineStr"/>
-      <c r="E104" s="9" t="inlineStr"/>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>Cumple parcialmente</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (contención de pasillo)</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7. PENDIENTE: el efecto en la eficiencia energética se cuantifica con el cálculo térmico de VAL-01</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
@@ -2676,9 +3164,21 @@
           <t>El recinto contará con detección temprana por aspiración de aire con tecnología láser, tipo AnaLASER o equivalente de prestaciones iguales o superiores.</t>
         </is>
       </c>
-      <c r="C105" s="9" t="inlineStr"/>
-      <c r="D105" s="9" t="inlineStr"/>
-      <c r="E105" s="9" t="inlineStr"/>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (detección temprana por aspiración de aire con tecnología láser)</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7 · T-11 ítem T11-30</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
@@ -2691,9 +3191,21 @@
           <t>La extinción será automática mediante agente limpio tipo FM-200 o equivalente, con aprobación UL e instalación conforme a norma NFPA.</t>
         </is>
       </c>
-      <c r="C106" s="9" t="inlineStr"/>
-      <c r="D106" s="9" t="inlineStr"/>
-      <c r="E106" s="9" t="inlineStr"/>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (extinción automática por agente limpio equivalente a FM-200, aprobación UL, instalación NFPA)</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7 · T-11 ítem T11-30</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
@@ -2706,9 +3218,21 @@
           <t>Se proveerá un sistema secundario de extintores portátiles habilitados, con mantención y certificación vigentes.</t>
         </is>
       </c>
-      <c r="C107" s="9" t="inlineStr"/>
-      <c r="D107" s="9" t="inlineStr"/>
-      <c r="E107" s="9" t="inlineStr"/>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (extintores portátiles certificados como sistema secundario)</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7 · T-11 ítem T11-30</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
@@ -2721,9 +3245,21 @@
           <t>El sistema de detección y extinción se integrará al monitoreo en línea y notificará al NOC y a la contraparte del CLIENTE.</t>
         </is>
       </c>
-      <c r="C108" s="9" t="inlineStr"/>
-      <c r="D108" s="9" t="inlineStr"/>
-      <c r="E108" s="9" t="inlineStr"/>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (detección y extinción integradas al monitoreo, con aviso al NOC y a la contraparte del CLIENTE)</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7 · T-11 ítem T11-30</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
@@ -2763,9 +3299,21 @@
           <t>Todo ingreso y egreso quedará registrado en una bitácora auditable, con identificación de la persona, fecha, hora y motivo, conservada por el período de retención declarado.</t>
         </is>
       </c>
-      <c r="C110" s="9" t="inlineStr"/>
-      <c r="D110" s="9" t="inlineStr"/>
-      <c r="E110" s="9" t="inlineStr"/>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (bitácora auditable de ingreso y egreso al recinto técnico)</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7 · T-11 ítem T11-31</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
@@ -2778,9 +3326,21 @@
           <t>Entre el acceso principal y el término del pasillo de la zona de control se dispondrá un espacio para la atención de personas en proceso de enrolamiento. Se evaluará mejor la existencia de una estación de enrolamiento fuera de las instalaciones del recinto técnico.</t>
         </is>
       </c>
-      <c r="C111" s="9" t="inlineStr"/>
-      <c r="D111" s="9" t="inlineStr"/>
-      <c r="E111" s="9" t="inlineStr"/>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (estación de enrolamiento en el acceso al recinto)</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7 · T-11 ítem T11-31</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
@@ -2793,9 +3353,21 @@
           <t>Al término del pasillo se instalará un acceso que impida el paso de más de una persona a la vez, con nueva verificación de identidad previa al ingreso.</t>
         </is>
       </c>
-      <c r="C112" s="9" t="inlineStr"/>
-      <c r="D112" s="9" t="inlineStr"/>
-      <c r="E112" s="9" t="inlineStr"/>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (mantrap de paso individual con nueva verificación de identidad)</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7 · T-11 ítem T11-31</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
@@ -2808,9 +3380,21 @@
           <t>El recinto contará con videovigilancia y monitoreo IP, con imágenes en línea y disponibles para visualización de al menos los últimos 30 días. Las grabaciones anteriores se respaldarán en un medio secundario recuperable y auditable.</t>
         </is>
       </c>
-      <c r="C113" s="9" t="inlineStr"/>
-      <c r="D113" s="9" t="inlineStr"/>
-      <c r="E113" s="9" t="inlineStr"/>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>Cumple parcialmente</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (videovigilancia IP con ≥30 días en línea)</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7 · T-11 ítem T11-31. PENDIENTE: el respaldo en medio secundario de las grabaciones anteriores a 30 días se define con VAL-01</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
@@ -2823,9 +3407,21 @@
           <t>El PROPONENTE declarará el procedimiento de acceso de terceros -fabricantes, mantenedores, auditores- con acompañamiento obligatorio y registro.</t>
         </is>
       </c>
-      <c r="C114" s="9" t="inlineStr"/>
-      <c r="D114" s="9" t="inlineStr"/>
-      <c r="E114" s="9" t="inlineStr"/>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>No aplica: procedimiento de acceso de terceros, acompañado, temporal, aprobado y registrado</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7 y 14</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
@@ -2838,9 +3434,21 @@
           <t>Se habi litará un servicio de custodia de medios de respaldo para el sitio primario, en un medio físico transportable a otro lugar cuando el CLIENTE lo determine. Se admite proponer una solución más segura y eficiente, debidamente justificada.</t>
         </is>
       </c>
-      <c r="C115" s="9" t="inlineStr"/>
-      <c r="D115" s="9" t="inlineStr"/>
-      <c r="E115" s="9" t="inlineStr"/>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (custodia de medios con copia transportable cuando el CLIENTE lo determine)</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7 y 13 · T-11 ítem T11-19</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
@@ -2868,9 +3476,21 @@
           <t>Se llevará un inventario de medios con rotación, verificación periódica de legibilidad y registro de todo movimiento de entrada y de salida.</t>
         </is>
       </c>
-      <c r="C117" s="9" t="inlineStr"/>
-      <c r="D117" s="9" t="inlineStr"/>
-      <c r="E117" s="9" t="inlineStr"/>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>Cumple parcialmente</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (inventario y custodia de medios con registro de movimientos)</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7 y 13. PENDIENTE: la rotación y la verificación periódica de legibilidad se desarrollan en el Subdoc. 10</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
@@ -2883,9 +3503,21 @@
           <t>El PROPONENTE habilitará el espacio físico necesario para el personal encargado de la operación y administración de la plataforma, con estaciones de trabajo, telefonía, conexión a Internet y todo elemento que permita realizar la labor en condiciones adecuadas.</t>
         </is>
       </c>
-      <c r="C118" s="9" t="inlineStr"/>
-      <c r="D118" s="9" t="inlineStr"/>
-      <c r="E118" s="9" t="inlineStr"/>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (4 puestos de operación en faena y 2 en el CIO, con monitores duales)</t>
+        </is>
+      </c>
+      <c r="E118" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7 y 8 · T-11 ítem T11-32</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
@@ -2898,9 +3530,21 @@
           <t>El espacio de operación estará separado de la sala de equipos y no requerirá el ingreso al recinto técnico para las labores habituales de operación.</t>
         </is>
       </c>
-      <c r="C119" s="9" t="inlineStr"/>
-      <c r="D119" s="9" t="inlineStr"/>
-      <c r="E119" s="9" t="inlineStr"/>
+      <c r="C119" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (espacio de operación separado de la sala de equipos, sin ingreso habitual al recinto)</t>
+        </is>
+      </c>
+      <c r="E119" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7 · Anexo A, contenedor K4</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
@@ -2928,9 +3572,21 @@
           <t>El acceso a las redes de comunicaciones estará provisto a través de rutas físicas distintas, con ingreso al edificio por puntos separados.</t>
         </is>
       </c>
-      <c r="C121" s="9" t="inlineStr"/>
-      <c r="D121" s="9" t="inlineStr"/>
-      <c r="E121" s="9" t="inlineStr"/>
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (dos carriers con rutas e ingresos físicos separados)</t>
+        </is>
+      </c>
+      <c r="E121" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7 y 16, VAL-06 · T-11 ítems T11-23 y T11-24</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
@@ -2943,9 +3599,21 @@
           <t>El PROPONENTE proveerá toda la conectividad, la seguridad y las canalizaciones, cañerías o duetos requeridos para cumplir los niveles de servicio comprometidos.</t>
         </is>
       </c>
-      <c r="C122" s="9" t="inlineStr"/>
-      <c r="D122" s="9" t="inlineStr"/>
-      <c r="E122" s="9" t="inlineStr"/>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (conectividad, seguridad y canalizaciones del recinto)</t>
+        </is>
+      </c>
+      <c r="E122" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7 y 15</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
@@ -2958,9 +3626,21 @@
           <t>Se privilegiará al PROPONENTE que ofrezca o provea especificaciones nuevas o mejores que las aquí establecidas, debidamente fundamentadas.</t>
         </is>
       </c>
-      <c r="C123" s="9" t="inlineStr"/>
-      <c r="D123" s="9" t="inlineStr"/>
-      <c r="E123" s="9" t="inlineStr"/>
+      <c r="C123" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>No aplica: regla de equivalencia. Todo modelo de referencia admite equivalente que cumpla o supere la ficha técnica</t>
+        </is>
+      </c>
+      <c r="E123" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 6 · T-11, hojas «Cómo usarlo» y «Fichas técnicas»</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="8" t="inlineStr">
@@ -2973,9 +3653,21 @@
           <t>El PROPONENTE declarará la modalidad escogida -activo-activo o activo-pasivo- y la justificará frente al costo, al RTO comprometido y a la complejidad operacional que introduce.</t>
         </is>
       </c>
-      <c r="C124" s="9" t="inlineStr"/>
-      <c r="D124" s="9" t="inlineStr"/>
-      <c r="E124" s="9" t="inlineStr"/>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (CIO Antofagasta en activo-pasivo, espera cálida)</t>
+        </is>
+      </c>
+      <c r="E124" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 8</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
@@ -2988,9 +3680,21 @@
           <t>El sitio secundario estará emplazado a una distancia suficiente del principal para no verse afectado por el mismo evento de fuerza mayor. El PROPONENTE declarará la distancia y el análisis de amenazas comunes considerado.</t>
         </is>
       </c>
-      <c r="C125" s="9" t="inlineStr"/>
-      <c r="D125" s="9" t="inlineStr"/>
-      <c r="E125" s="9" t="inlineStr"/>
+      <c r="C125" s="9" t="inlineStr">
+        <is>
+          <t>Cumple parcialmente</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (CIO a 145 km de la faena, sin evento físico común inmediato)</t>
+        </is>
+      </c>
+      <c r="E125" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 8. PENDIENTE: el análisis formal de amenazas comunes a ambos sitios se cierra con VAL-01</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="8" t="inlineStr">
@@ -3003,9 +3707,21 @@
           <t>La replicación de datos será continua, con medición y alertamiento del retraso de replicación.</t>
         </is>
       </c>
-      <c r="C126" s="9" t="inlineStr"/>
-      <c r="D126" s="9" t="inlineStr"/>
-      <c r="E126" s="9" t="inlineStr"/>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (réplica continua cifrada con medición y alerta de retraso)</t>
+        </is>
+      </c>
+      <c r="E126" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 8 y 12 · T-11 ítems T11-05 y T11-06</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
@@ -3045,9 +3761,21 @@
           <t>El procedimiento de conmutación estará documentado, automatizado en la mayor medida posible y ejecutable por el personal del CLIENTE tras la transferencia de conocimiento.</t>
         </is>
       </c>
-      <c r="C128" s="9" t="inlineStr"/>
-      <c r="D128" s="9" t="inlineStr"/>
-      <c r="E128" s="9" t="inlineStr"/>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (declaración de desastre, fencing del primario, promoción única y validación sintética)</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 8</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
@@ -3060,9 +3788,21 @@
           <t>Existirá un procedimiento de retorno al sitio principal igualmente documentado y probado, con reconciliación de los datos generados durante la contingencia.</t>
         </is>
       </c>
-      <c r="C129" s="9" t="inlineStr"/>
-      <c r="D129" s="9" t="inlineStr"/>
-      <c r="E129" s="9" t="inlineStr"/>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (retorno al primario con reconciliación y prevención de split-brain)</t>
+        </is>
+      </c>
+      <c r="E129" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 8 y 17</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="8" t="inlineStr">
@@ -3075,9 +3815,21 @@
           <t>El plan de recuperación ante desastres se probará al menos dos veces al año mediante conmutación real, con informe de resultados, medición del RTO y del RPO efectivamente alcanzados y plan de corrección de las brechas detectadas.</t>
         </is>
       </c>
-      <c r="C130" s="9" t="inlineStr"/>
-      <c r="D130" s="9" t="inlineStr"/>
-      <c r="E130" s="9" t="inlineStr"/>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (conmutación real dos veces al año con medición de RTO y RPO y plan de corrección)</t>
+        </is>
+      </c>
+      <c r="E130" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 8</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
@@ -3090,11 +3842,19 @@
           <t>Se valorará que la conmutación sea automática ante la detección de indisponibilidad, 1 con criterio de disparo declarado y protección contra conmutación innecesaria.</t>
         </is>
       </c>
-      <c r="C131" s="9" t="inlineStr"/>
-      <c r="D131" s="9" t="inlineStr"/>
+      <c r="C131" s="9" t="inlineStr">
+        <is>
+          <t>Cumple parcialmente</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (promoción única, deliberadamente manual)</t>
+        </is>
+      </c>
       <c r="E131" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.2 — Arquitectura física (Grupo 3)</t>
+          <t>Subdoc. 4.2 v1.1, ap. 8. La conmutación automática no se ofrece por decisión de diseño: el disparo lo declara el jefe de incidente, precisamente para evitar la conmutación innecesaria y el split-brain que el propio requisito manda proteger</t>
         </is>
       </c>
     </row>
@@ -3109,9 +3869,21 @@
           <t>La política de respaldo seguirá el esquema 3-2-1-1-0: tres copias, en dos medios distintos, una fuera de sitio, una inmutable o fuera de línea y cero errores de verificación de restauración.</t>
         </is>
       </c>
-      <c r="C132" s="9" t="inlineStr"/>
-      <c r="D132" s="9" t="inlineStr"/>
-      <c r="E132" s="9" t="inlineStr"/>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (esquema 3-2-1-1-0)</t>
+        </is>
+      </c>
+      <c r="E132" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 13 · T-11 ítem T11-19</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
@@ -3124,9 +3896,21 @@
           <t>Los respaldos estarán cifrados en reposo y en tránsito, con clave gestionada de forma independiente de la infraestructura respaldada.</t>
         </is>
       </c>
-      <c r="C133" s="9" t="inlineStr"/>
-      <c r="D133" s="9" t="inlineStr"/>
-      <c r="E133" s="9" t="inlineStr"/>
+      <c r="C133" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (respaldo cifrado con llaves y cuentas independientes de la infraestructura respaldada)</t>
+        </is>
+      </c>
+      <c r="E133" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 13 · T-11 ítem T11-12</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="8" t="inlineStr">
@@ -3139,9 +3923,21 @@
           <t>Las copias inmutables estarán protegidas contra borrado y contra modificación durante su período de retención, incluso frente a credenciales administrativas comprometidas.</t>
         </is>
       </c>
-      <c r="C134" s="9" t="inlineStr"/>
-      <c r="D134" s="9" t="inlineStr"/>
-      <c r="E134" s="9" t="inlineStr"/>
+      <c r="C134" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (repositorio inmutable con credenciales separadas y bloqueo de objeto)</t>
+        </is>
+      </c>
+      <c r="E134" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 13 · T-11 ítems T11-08 y T11-19</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
@@ -3154,9 +3950,21 @@
           <t>Se ejecutará y documentará una prueba de restauración al menos mensual, sobre una muestra representativa, con medición del tiempo efectivo de restauración.</t>
         </is>
       </c>
-      <c r="C135" s="9" t="inlineStr"/>
-      <c r="D135" s="9" t="inlineStr"/>
-      <c r="E135" s="9" t="inlineStr"/>
+      <c r="C135" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (restauración mensual por muestra y recuperación completa semestral)</t>
+        </is>
+      </c>
+      <c r="E135" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 13</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="8" t="inlineStr">
@@ -3169,9 +3977,21 @@
           <t>El PROPONENTE declarará, por cada dominio de datos, la frecuencia de respaldo, el período de retención y el tiempo estimado de restauración completa.</t>
         </is>
       </c>
-      <c r="C136" s="9" t="inlineStr"/>
-      <c r="D136" s="9" t="inlineStr"/>
-      <c r="E136" s="9" t="inlineStr"/>
+      <c r="C136" s="9" t="inlineStr">
+        <is>
+          <t>Cumple parcialmente</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base; retención por dominio declarada en el modelo de datos</t>
+        </is>
+      </c>
+      <c r="E136" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 5 v2.1, ap. 6.2 · Subdoc. 4.2 v1.1, ap. 13. PENDIENTE: la frecuencia de respaldo y el tiempo estimado de restauración completa por dominio se cierran con VAL-05</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
@@ -3199,9 +4019,21 @@
           <t>El PROPONENTE especificará el equipamiento de cómputo con su marca, modelo de referencia, procesador, memoria, almacenamiento local, interfaces y consumo, junto con el cálculo de dimensionamiento que lo sustenta.</t>
         </is>
       </c>
-      <c r="C138" s="9" t="inlineStr"/>
-      <c r="D138" s="9" t="inlineStr"/>
-      <c r="E138" s="9" t="inlineStr"/>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (servidores de faena y del CIO, con su cálculo de dimensionamiento)</t>
+        </is>
+      </c>
+      <c r="E138" s="9" t="inlineStr">
+        <is>
+          <t>T-11 ítems T11-15 a T11-19 y hoja «Dimensionamiento» · Subdoc. 4.2 v1.1, ap. 7, 8 y 12</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
@@ -3214,9 +4046,21 @@
           <t>El almacenamiento será redundante, con tolerancia declarada a la falla de discos, control de errores y monitoreo predictivo de salud de los medios.</t>
         </is>
       </c>
-      <c r="C139" s="9" t="inlineStr"/>
-      <c r="D139" s="9" t="inlineStr"/>
-      <c r="E139" s="9" t="inlineStr"/>
+      <c r="C139" s="9" t="inlineStr">
+        <is>
+          <t>Cumple parcialmente</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (RAID6 de doble controladora con hot spare en sala; RAID1 en borde)</t>
+        </is>
+      </c>
+      <c r="E139" s="9" t="inlineStr">
+        <is>
+          <t>T-11 ítems T11-17, T11-18 y T11-33 · Subdoc. 4.2 v1.1, ap. 7, 9 y 13. PENDIENTE: el monitoreo predictivo de salud de los medios se declara en el Subdoc. 10</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="8" t="inlineStr">
@@ -3229,9 +4073,21 @@
           <t>Los conmutadores de núcleo, los cortafuegos y los balanceadores de carga estarán en configuración de alta disponibilidad, sin punto único de falla.</t>
         </is>
       </c>
-      <c r="C140" s="9" t="inlineStr"/>
-      <c r="D140" s="9" t="inlineStr"/>
-      <c r="E140" s="9" t="inlineStr"/>
+      <c r="C140" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (core, NGFW y routers de borde en pares de alta disponibilidad)</t>
+        </is>
+      </c>
+      <c r="E140" s="9" t="inlineStr">
+        <is>
+          <t>T-11 ítems T11-20 a T11-22 · Subdoc. 4.2 v1.1, ap. 4 y 13</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
@@ -3244,9 +4100,21 @@
           <t>Todo el equipamiento contará con fuentes de poder redundantes y conexión a circuitos eléctricos distintos.</t>
         </is>
       </c>
-      <c r="C141" s="9" t="inlineStr"/>
-      <c r="D141" s="9" t="inlineStr"/>
-      <c r="E141" s="9" t="inlineStr"/>
+      <c r="C141" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (doble fuente de poder y circuitos A/B independientes)</t>
+        </is>
+      </c>
+      <c r="E141" s="9" t="inlineStr">
+        <is>
+          <t>T-11 ítems T11-15, T11-16 y T11-27 · Subdoc. 4.2 v1.1, ap. 7</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="8" t="inlineStr">
@@ -3286,9 +4154,21 @@
           <t>El equipamiento será nuevo, sin uso previo, con garantía de fábrica vigente desde la 1 recepción conforme.</t>
         </is>
       </c>
-      <c r="C143" s="9" t="inlineStr"/>
-      <c r="D143" s="9" t="inlineStr"/>
-      <c r="E143" s="9" t="inlineStr"/>
+      <c r="C143" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="inlineStr">
+        <is>
+          <t>No aplica: condición de suministro de todo el equipamiento ofertado</t>
+        </is>
+      </c>
+      <c r="E143" s="9" t="inlineStr">
+        <is>
+          <t>T-11, hoja «Fichas técnicas» · Subdoc. 4.2 v1.1, ap. 15</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="8" t="inlineStr">
@@ -3301,9 +4181,21 @@
           <t>El PROPONENTE especificará las estaciones de trabajo requeridas para la operación y la administración de la plataforma, en la cantidad que determine el dimensionamiento del caso, con monitores duales.</t>
         </is>
       </c>
-      <c r="C144" s="9" t="inlineStr"/>
-      <c r="D144" s="9" t="inlineStr"/>
-      <c r="E144" s="9" t="inlineStr"/>
+      <c r="C144" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (6 estaciones de administración con monitores duales: 4 en faena, 2 en el CIO)</t>
+        </is>
+      </c>
+      <c r="E144" s="9" t="inlineStr">
+        <is>
+          <t>T-11 ítem T11-32 · Subdoc. 4.2 v1.1, ap. 7 y 8</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
@@ -3331,9 +4223,21 @@
           <t>Las estaciones estarán gestionadas de forma centralizada, con cifrado de disco, control de dispositivos extraíbles, antivirus con detección y respuesta y actualización automatizada.</t>
         </is>
       </c>
-      <c r="C146" s="9" t="inlineStr"/>
-      <c r="D146" s="9" t="inlineStr"/>
-      <c r="E146" s="9" t="inlineStr"/>
+      <c r="C146" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (gestión centralizada, cifrado de disco, control de dispositivos extraíbles y EDR)</t>
+        </is>
+      </c>
+      <c r="E146" s="9" t="inlineStr">
+        <is>
+          <t>T-11 ítem T11-32 · Subdoc. 4.2 v1.1, ap. 14</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
@@ -3373,9 +4277,21 @@
           <t>La especificación considerará las condiciones reales de uso del caso: intemperie, humedad, polvo, vibración, temperatura, uso con guantes, luminosidad y autonomía de batería requerida por turno.</t>
         </is>
       </c>
-      <c r="C148" s="9" t="inlineStr"/>
-      <c r="D148" s="9" t="inlineStr"/>
-      <c r="E148" s="9" t="inlineStr"/>
+      <c r="C148" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="inlineStr">
+        <is>
+          <t>C-03 — Captura en terreno (tabletas rugerizadas para intemperie, guantes, sol directo y turno de 12 horas)</t>
+        </is>
+      </c>
+      <c r="E148" s="9" t="inlineStr">
+        <is>
+          <t>T-11 ítem T11-38 · Subdoc. 4.2 v1.1, ap. 9.1</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
@@ -3388,9 +4304,21 @@
           <t>Los dispositivos declararán su grado de protección contra polvo y agua y su resistencia a caídas, coherentes con el entorno de operación.</t>
         </is>
       </c>
-      <c r="C149" s="9" t="inlineStr"/>
-      <c r="D149" s="9" t="inlineStr"/>
-      <c r="E149" s="9" t="inlineStr"/>
+      <c r="C149" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>C-03 — Captura en terreno (IP65 y caída ≥1,2 m)</t>
+        </is>
+      </c>
+      <c r="E149" s="9" t="inlineStr">
+        <is>
+          <t>T-11 ítem T11-38 · Subdoc. 4.2 v1.1, ap. 9.1</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="8" t="inlineStr">
@@ -3403,9 +4331,21 @@
           <t>El PROPONENTE indicará el ciclo de vida esperado de cada dispositivo, la disponibilidad de repuestos y el plan de reposición durante los 56 meses del Contrato.</t>
         </is>
       </c>
-      <c r="C150" s="9" t="inlineStr"/>
-      <c r="D150" s="9" t="inlineStr"/>
-      <c r="E150" s="9" t="inlineStr"/>
+      <c r="C150" s="9" t="inlineStr">
+        <is>
+          <t>Cumple parcialmente</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="inlineStr">
+        <is>
+          <t>C-03 — Captura en terreno; C-04 — Nodo de borde</t>
+        </is>
+      </c>
+      <c r="E150" s="9" t="inlineStr">
+        <is>
+          <t>T-11, hoja «Fichas técnicas» · Subdoc. 4.2 v1.1, ap. 14. PENDIENTE: el plan de reposición a lo largo de los 56 meses se cuantifica en la Oferta Económica</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
@@ -3460,9 +4400,21 @@
           <t>El PROPONENTE presentará el plan de ciclo de vida del equipamiento: recepción, puesta en servicio, mantención, actualización, retiro y disposición final.</t>
         </is>
       </c>
-      <c r="C153" s="9" t="inlineStr"/>
-      <c r="D153" s="9" t="inlineStr"/>
-      <c r="E153" s="9" t="inlineStr"/>
+      <c r="C153" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>No aplica: plan de ciclo de vida del equipamiento</t>
+        </is>
+      </c>
+      <c r="E153" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 14</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="8" t="inlineStr">
@@ -3475,9 +4427,21 @@
           <t>Todo medio de almacenamiento que salga de servicio será borrado de forma segura y verificable, con certificado de destrucción o de sanitización entregado al CLIENTE.</t>
         </is>
       </c>
-      <c r="C154" s="9" t="inlineStr"/>
-      <c r="D154" s="9" t="inlineStr"/>
-      <c r="E154" s="9" t="inlineStr"/>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="inlineStr">
+        <is>
+          <t>No aplica: sanitización verificable con certificado al CLIENTE</t>
+        </is>
+      </c>
+      <c r="E154" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 14 · Subdoc. 5 v2.1, ap. 6.4</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
@@ -3490,9 +4454,21 @@
           <t>La disposición final de equipamiento electrónico se realizará con gestor autorizado, conforme a la normativa de residuos aplicable, con certificado de disposición.</t>
         </is>
       </c>
-      <c r="C155" s="9" t="inlineStr"/>
-      <c r="D155" s="9" t="inlineStr"/>
-      <c r="E155" s="9" t="inlineStr"/>
+      <c r="C155" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>No aplica: disposición final con gestor autorizado y certificado</t>
+        </is>
+      </c>
+      <c r="E155" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 14</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="8" t="inlineStr">
@@ -3856,9 +4832,21 @@
           <t>Se ejecutarán pruebas de resiliencia mediante inyección controlada de fallas -caída de instancia, de zona, de dependencia externa, latencia elevada, saturación de disco- antes de cada paso a producción y al menos una vez por semestre durante la Operación.</t>
         </is>
       </c>
-      <c r="C173" s="9" t="inlineStr"/>
-      <c r="D173" s="9" t="inlineStr"/>
-      <c r="E173" s="9" t="inlineStr"/>
+      <c r="C173" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (inyección controlada de falla en las pruebas de conmutación)</t>
+        </is>
+      </c>
+      <c r="E173" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 8</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="8" t="inlineStr">
@@ -3871,9 +4859,21 @@
           <t>El PROPONENTE documentará, por cada dependencia externa, el comportamiento de la solución cuando esa dependencia no responde, responde con error o responde con lentitud.</t>
         </is>
       </c>
-      <c r="C174" s="9" t="inlineStr"/>
-      <c r="D174" s="9" t="inlineStr"/>
-      <c r="E174" s="9" t="inlineStr"/>
+      <c r="C174" s="9" t="inlineStr">
+        <is>
+          <t>Cumple</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="inlineStr">
+        <is>
+          <t>Los siete adaptadores C-09 a C-14 y el adaptador de control de fatiga</t>
+        </is>
+      </c>
+      <c r="E174" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 5 v2.1, ap. 4.5 · Subdoc. 4.2 v1.1, ap. 11</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="8" t="inlineStr">
@@ -5395,9 +6395,21 @@
           <t>El PROPONENTE dimensionará la infraestructura ajustada a la demanda real, evitando capacidad ociosa permanente, y declarará el factor de utilización proyectado.</t>
         </is>
       </c>
-      <c r="C238" s="9" t="inlineStr"/>
-      <c r="D238" s="9" t="inlineStr"/>
-      <c r="E238" s="9" t="inlineStr"/>
+      <c r="C238" s="9" t="inlineStr">
+        <is>
+          <t>Cumple parcialmente</t>
+        </is>
+      </c>
+      <c r="D238" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base</t>
+        </is>
+      </c>
+      <c r="E238" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 12 y 16, VAL-05, con gatillo de expansión al 70 % sostenido. PENDIENTE: el factor de utilización proyectado se declara con el perfil de carga real de VAL-05</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="8" t="inlineStr">
@@ -5452,9 +6464,21 @@
           <t>Se declarará la eficiencia en el uso de la energía (PUE) del recinto on-premise y la intensidad de carbono de la región de nube escogida.</t>
         </is>
       </c>
-      <c r="C241" s="9" t="inlineStr"/>
-      <c r="D241" s="9" t="inlineStr"/>
-      <c r="E241" s="9" t="inlineStr"/>
+      <c r="C241" s="9" t="inlineStr">
+        <is>
+          <t>Cumple parcialmente</t>
+        </is>
+      </c>
+      <c r="D241" s="9" t="inlineStr">
+        <is>
+          <t>C-22 — Plataforma base (PUE objetivo ≤1,55 del recinto de faena)</t>
+        </is>
+      </c>
+      <c r="E241" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 4.2 v1.1, ap. 7. PENDIENTE: la intensidad de carbono de Azure Chile Central se declara con el dato publicado del proveedor</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="8" t="inlineStr">
@@ -7581,9 +8605,21 @@
           <t>Información institucional: descripción detallada del giro principal, historia y trayectoria de la empresa con al menos tres años de antigüedad comprobable, misión, visión y valores, certificaciones y acreditaciones vigentes, y presencia geográfica y oficinas.</t>
         </is>
       </c>
-      <c r="C348" s="9" t="inlineStr"/>
-      <c r="D348" s="9" t="inlineStr"/>
-      <c r="E348" s="9" t="inlineStr"/>
+      <c r="C348" s="9" t="inlineStr">
+        <is>
+          <t>Cumple parcialmente</t>
+        </is>
+      </c>
+      <c r="D348" s="9" t="inlineStr">
+        <is>
+          <t>No aplica: información institucional del PROPONENTE</t>
+        </is>
+      </c>
+      <c r="E348" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 1 v1.0, ap. 2 y 6. PENDIENTE: el sitio corporativo es simulado para el ejercicio académico (dominio .example) y no está activo; el contenido exigido está íntegro en el subdocumento</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="8" t="inlineStr">
@@ -7596,9 +8632,21 @@
           <t>años, casos documentados con métricas verificables, testimonios de clientes con autorización de publicación, industrias atendidas con énfasis en la del caso asignado, y volumen de transacciones o de personas usuarias gestionadas.</t>
         </is>
       </c>
-      <c r="C349" s="9" t="inlineStr"/>
-      <c r="D349" s="9" t="inlineStr"/>
-      <c r="E349" s="9" t="inlineStr"/>
+      <c r="C349" s="9" t="inlineStr">
+        <is>
+          <t>Cumple parcialmente</t>
+        </is>
+      </c>
+      <c r="D349" s="9" t="inlineStr">
+        <is>
+          <t>No aplica: experiencia y casos de éxito del PROPONENTE</t>
+        </is>
+      </c>
+      <c r="E349" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 1 v1.0, ap. 8 y 9 · Formulario T-6 v1.0. PENDIENTE: publicación en sitio activo; los tres proyectos son simulados y están rotulados como tales</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="8" t="inlineStr">
@@ -7611,9 +8659,21 @@
           <t>Equipo profesional: organigrama del equipo directivo, perfiles de socios y directores, currículos resumidos del equipo técnico clave y certificaciones profesionales del personal.</t>
         </is>
       </c>
-      <c r="C350" s="9" t="inlineStr"/>
-      <c r="D350" s="9" t="inlineStr"/>
-      <c r="E350" s="9" t="inlineStr"/>
+      <c r="C350" s="9" t="inlineStr">
+        <is>
+          <t>Cumple parcialmente</t>
+        </is>
+      </c>
+      <c r="D350" s="9" t="inlineStr">
+        <is>
+          <t>No aplica: equipo profesional del PROPONENTE</t>
+        </is>
+      </c>
+      <c r="E350" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 1 v1.0, ap. 5, 5.1 y 6. PENDIENTE: publicación en sitio activo; la asignación nominal y la evidencia de certificaciones corresponden al Formulario T-8</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="8" t="inlineStr">
@@ -7626,9 +8686,21 @@
           <t>Capacidades técnicas: servicios y soluciones ofrecidas, conjunto tecnológico dominado, alianzas tecnológicas con proveedores de nube y de plataforma, metodologías de trabajo certificadas, e infraestructura y capacidad instalada.</t>
         </is>
       </c>
-      <c r="C351" s="9" t="inlineStr"/>
-      <c r="D351" s="9" t="inlineStr"/>
-      <c r="E351" s="9" t="inlineStr"/>
+      <c r="C351" s="9" t="inlineStr">
+        <is>
+          <t>Cumple parcialmente</t>
+        </is>
+      </c>
+      <c r="D351" s="9" t="inlineStr">
+        <is>
+          <t>No aplica: capacidades técnicas y alianzas del PROPONENTE</t>
+        </is>
+      </c>
+      <c r="E351" s="9" t="inlineStr">
+        <is>
+          <t>Subdoc. 1 v1.0, ap. 3, 4 y 7. PENDIENTE: publicación en sitio activo</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="8" t="inlineStr">
@@ -14369,7 +15441,7 @@
       <c r="E2" s="9" t="inlineStr"/>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G2" s="9" t="inlineStr">
@@ -14379,7 +15451,7 @@
       </c>
       <c r="H2" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 4 y 17</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 1.3 y 5</t>
         </is>
       </c>
     </row>
@@ -14407,7 +15479,7 @@
       <c r="E3" s="9" t="inlineStr"/>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
@@ -14417,7 +15489,7 @@
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 3.3 y 6</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 4.2, 4.3 y 7</t>
         </is>
       </c>
     </row>
@@ -14445,7 +15517,7 @@
       <c r="E4" s="9" t="inlineStr"/>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
@@ -14455,7 +15527,7 @@
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 1.1</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 1.1</t>
         </is>
       </c>
     </row>
@@ -14483,7 +15555,7 @@
       <c r="E5" s="9" t="inlineStr"/>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
@@ -14493,7 +15565,7 @@
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 1.2 y 18</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 1.2 y 21</t>
         </is>
       </c>
     </row>
@@ -14521,7 +15593,7 @@
       <c r="E6" s="9" t="inlineStr"/>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
@@ -14531,7 +15603,7 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 4 capa 4 y 10</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 5, capa 4</t>
         </is>
       </c>
     </row>
@@ -14559,7 +15631,7 @@
       <c r="E7" s="9" t="inlineStr"/>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
@@ -14569,7 +15641,7 @@
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 8.3 y 10</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 10.3 y 12.2</t>
         </is>
       </c>
     </row>
@@ -14597,7 +15669,7 @@
       <c r="E8" s="9" t="inlineStr"/>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -14607,7 +15679,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 4 capa 5 y 10</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 5, capa 5</t>
         </is>
       </c>
     </row>
@@ -14635,7 +15707,7 @@
       <c r="E9" s="9" t="inlineStr"/>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
@@ -14645,7 +15717,7 @@
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 10</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 12.4</t>
         </is>
       </c>
     </row>
@@ -14673,7 +15745,7 @@
       <c r="E10" s="9" t="inlineStr"/>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
@@ -14683,7 +15755,7 @@
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 9.4 y 10</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 11.5</t>
         </is>
       </c>
     </row>
@@ -14711,7 +15783,7 @@
       <c r="E11" s="9" t="inlineStr"/>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
@@ -14721,7 +15793,7 @@
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 10 y 13.1</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 12.2</t>
         </is>
       </c>
     </row>
@@ -14749,7 +15821,7 @@
       <c r="E12" s="9" t="inlineStr"/>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -14759,7 +15831,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 10.2</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 12.5</t>
         </is>
       </c>
     </row>
@@ -14787,7 +15859,7 @@
       <c r="E13" s="9" t="inlineStr"/>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -14797,7 +15869,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 7</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 9</t>
         </is>
       </c>
     </row>
@@ -14825,7 +15897,7 @@
       <c r="E14" s="9" t="inlineStr"/>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
@@ -14835,7 +15907,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 8.1, 10 y 13.8</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 10.1 y 15.6</t>
         </is>
       </c>
     </row>
@@ -14873,7 +15945,7 @@
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -14911,7 +15983,7 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -14949,7 +16021,7 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -14977,7 +16049,7 @@
       <c r="E18" s="9" t="inlineStr"/>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
@@ -14987,7 +16059,7 @@
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 11.4 y 13.8</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 13.1 y 13.3</t>
         </is>
       </c>
     </row>
@@ -15025,7 +16097,7 @@
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -15063,7 +16135,7 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -15091,7 +16163,7 @@
       <c r="E21" s="9" t="inlineStr"/>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
@@ -15101,7 +16173,7 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 13.8</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 15.6</t>
         </is>
       </c>
     </row>
@@ -15139,7 +16211,7 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -15177,7 +16249,7 @@
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -15205,7 +16277,7 @@
       <c r="E24" s="9" t="inlineStr"/>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
@@ -15215,7 +16287,7 @@
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 9 y 9.1</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 11.1 y 11.3</t>
         </is>
       </c>
     </row>
@@ -15253,7 +16325,7 @@
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -15291,7 +16363,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -15319,7 +16391,7 @@
       <c r="E27" s="9" t="inlineStr"/>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
@@ -15329,7 +16401,7 @@
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 4 capa 8 y 12.1</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 5 capa 8, y 14.1</t>
         </is>
       </c>
     </row>
@@ -15367,7 +16439,7 @@
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -15395,7 +16467,7 @@
       <c r="E29" s="9" t="inlineStr"/>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
@@ -15405,7 +16477,7 @@
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 13.6</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 15.4</t>
         </is>
       </c>
     </row>
@@ -15433,7 +16505,7 @@
       <c r="E30" s="9" t="inlineStr"/>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
@@ -15443,7 +16515,7 @@
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 13.7</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 15.5</t>
         </is>
       </c>
     </row>
@@ -15481,7 +16553,7 @@
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -15519,7 +16591,7 @@
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -15557,7 +16629,7 @@
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -15589,7 +16661,7 @@
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
@@ -15599,7 +16671,7 @@
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>El caso usa RT-03.24 para el estudio de cobertura inalámbrica, que en el transversal es RT-03.23. El RT-03.24 transversal trata de calidad de servicio y priorización de tráfico. · PARCIALMENTE RESUELTO en Subdoc. 4.1 v3.0, apartados 4 capa 3 y 14.1</t>
+          <t>El caso usa RT-03.24 para el estudio de cobertura inalámbrica, que en el transversal es RT-03.23. El RT-03.24 transversal trata de calidad de servicio y priorización de tráfico. · PARCIALMENTE RESUELTO en Subdoc. 4.1 v4.2, ap. 5 capa 3 y 12.6 — la calidad de servicio y la priorización de tráfico se declaran ahí; el estudio de cobertura del rajo, con zonas de sombra y proyección a tres años, es del Subdoc. 4.2.</t>
         </is>
       </c>
     </row>
@@ -15637,7 +16709,7 @@
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -15675,7 +16747,7 @@
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -15713,7 +16785,7 @@
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -15751,7 +16823,7 @@
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -15789,7 +16861,7 @@
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -15827,7 +16899,7 @@
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -15855,7 +16927,7 @@
       <c r="E41" s="9" t="inlineStr"/>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
@@ -15865,7 +16937,7 @@
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 13.5</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 15.3</t>
         </is>
       </c>
     </row>
@@ -15893,7 +16965,7 @@
       <c r="E42" s="9" t="inlineStr"/>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -15903,7 +16975,7 @@
       </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 13.3</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 15.1</t>
         </is>
       </c>
     </row>
@@ -15941,7 +17013,7 @@
       </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -15969,7 +17041,7 @@
       <c r="E44" s="9" t="inlineStr"/>
       <c r="F44" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
@@ -15979,7 +17051,7 @@
       </c>
       <c r="H44" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 13.5</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 15.3</t>
         </is>
       </c>
     </row>
@@ -16017,7 +17089,7 @@
       </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -16055,7 +17127,7 @@
       </c>
       <c r="H46" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -16093,7 +17165,7 @@
       </c>
       <c r="H47" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -16131,7 +17203,7 @@
       </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -16167,7 +17239,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="H49" s="9" t="inlineStr"/>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 5 v2.1, ap. 1.2 y 1.6 · anexo Diccionario_Datos v2.1, hojas «Diccionario» y «Entidades»</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
@@ -16201,7 +17277,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="H50" s="9" t="inlineStr"/>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 5 v2.1, ap. 2.1 a 2.4 · anexo Diccionario_Datos v2.1, hoja «Dominios»</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -16235,7 +17315,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="H51" s="9" t="inlineStr"/>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 5 v2.1, ap. 2.3 y 6.5 · anexo Diccionario_Datos v2.1, entidad Asiento de auditoría</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -16269,7 +17353,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="H52" s="9" t="inlineStr"/>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 5 v2.1, ap. 6.1</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -16305,7 +17393,7 @@
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
-          <t>La decisión lógica queda declarada en Subdoc. 4.1 v3.0, ap. 4 capa 6 y ADR-08; el detalle propio de este entregable se mantiene aquí.</t>
+          <t>La decisión lógica queda declarada en Subdoc. 4.1 v4.2, ap. 5 capa 6, y ADR-08 del ap. 21; el detalle propio de este entregable se mantiene aquí.</t>
         </is>
       </c>
     </row>
@@ -16341,7 +17429,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="H54" s="9" t="inlineStr"/>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 5 v2.1, ap. 5.4 y 6.4</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -16375,7 +17467,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="H55" s="9" t="inlineStr"/>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 5 v2.1, ap. 1.3 y 6.5</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
@@ -16409,7 +17505,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="H56" s="9" t="inlineStr"/>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 5 v2.1, ap. 1.4</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
@@ -16443,7 +17543,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="H57" s="9" t="inlineStr"/>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 5 v2.1, ap. 3.2, fases 1 y 2</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
@@ -16477,7 +17581,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="H58" s="9" t="inlineStr"/>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 5 v2.1, ap. 3.2, fase 3, y ap. 3.3</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
@@ -16511,7 +17619,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="H59" s="9" t="inlineStr"/>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 5 v2.1, ap. 3.2, fase 5, y ap. 3.3</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
@@ -16547,7 +17659,7 @@
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
-          <t>La decisión lógica queda declarada en Subdoc. 4.1 v3.0, ap. 4 capa 3 y 8.3; el detalle propio de este entregable se mantiene aquí.</t>
+          <t>La decisión lógica queda declarada en Subdoc. 4.1 v4.2, ap. 5 capa 3, y 10.3; el detalle propio de este entregable se mantiene aquí.</t>
         </is>
       </c>
     </row>
@@ -16585,7 +17697,7 @@
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
-          <t>La decisión lógica queda declarada en Subdoc. 4.1 v3.0, ap. 8.3; el detalle propio de este entregable se mantiene aquí.</t>
+          <t>La decisión lógica queda declarada en Subdoc. 4.1 v4.2, ap. 10.3; el detalle propio de este entregable se mantiene aquí.</t>
         </is>
       </c>
     </row>
@@ -16623,7 +17735,7 @@
       </c>
       <c r="H62" s="9" t="inlineStr">
         <is>
-          <t>La decisión lógica queda declarada en Subdoc. 4.1 v3.0, ap. 4 capa 3 y 8.3; el detalle propio de este entregable se mantiene aquí.</t>
+          <t>La decisión lógica queda declarada en Subdoc. 4.1 v4.2, ap. 5 capa 3, y 10.3; el detalle propio de este entregable se mantiene aquí.</t>
         </is>
       </c>
     </row>
@@ -16661,7 +17773,7 @@
       </c>
       <c r="H63" s="9" t="inlineStr">
         <is>
-          <t>La decisión lógica queda declarada en Subdoc. 4.1 v3.0, ap. 8.3 y 12.1; el detalle propio de este entregable se mantiene aquí.</t>
+          <t>La decisión lógica queda declarada en Subdoc. 4.1 v4.2, ap. 10.3 y 14.1; el detalle propio de este entregable se mantiene aquí.</t>
         </is>
       </c>
     </row>
@@ -16697,7 +17809,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="H64" s="9" t="inlineStr"/>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 5 v2.1, ap. 1.5</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
@@ -16731,7 +17847,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="H65" s="9" t="inlineStr"/>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE RESUELTO en Subdoc. 5 v2.1, ap. 1.5 y 4.5. PENDIENTE: la ventana de disponibilidad de cada sistema contraparte se cierra con la Consulta N.º 5 y con el levantamiento VAL-03 del Subdoc. 4.2</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
@@ -16765,7 +17885,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="H66" s="9" t="inlineStr"/>
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE RESUELTO en Subdoc. 5 v2.1, ap. 3.2, fase 4, con cuarentena por registro y motivo de lista cerrada. PENDIENTE: la carga y descarga masiva como función de operación se desarrolla con la familia RF-ADM del catálogo</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
@@ -16833,7 +17957,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="H68" s="9" t="inlineStr"/>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 5 v2.1, ap. 5.1 y 5.4</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
@@ -16867,7 +17995,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="H69" s="9" t="inlineStr"/>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 5 v2.1, ap. 5.2 y 5.3</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
@@ -16901,7 +18033,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="H70" s="9" t="inlineStr"/>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 5 v2.1, ap. 5.3 y 5.4</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
@@ -16935,7 +18071,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="H71" s="9" t="inlineStr"/>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE RESUELTO en Subdoc. 5 v2.1, ap. 5.4. PENDIENTE: la programación de envío por calendario se desarrolla con la familia RF-ANA del catálogo</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
@@ -17009,7 +18149,7 @@
       </c>
       <c r="H73" s="9" t="inlineStr">
         <is>
-          <t>El caso usa RT-06.01 para la tipología del emplazamiento on-premise. En el transversal, la tipología es la tabla sin código del numeral 6.1; RT-06.01 exige que el espacio asignado sea de uso exclusivo y aislado, con acceso independiente.</t>
+          <t>El caso usa RT-06.01 para la tipología del emplazamiento on-premise. En el transversal, la tipología es la tabla sin código del numeral 6.1; RT-06.01 exige que el espacio asignado sea de uso exclusivo y aislado, con acceso independiente. · RESUELTO en Subdoc. 4.2 v1.1, ap. 7 y 8</t>
         </is>
       </c>
     </row>
@@ -17079,7 +18219,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H75" s="9" t="inlineStr"/>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE RESUELTO en Subdoc. 4.2 v1.1, ap. 7 y Anexo A, lámina B. PENDIENTE: el plano de distribución interna se emite tras el levantamiento VAL-01</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
@@ -17147,7 +18291,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H77" s="9" t="inlineStr"/>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 7 y 8 · T-11 ítems T11-25 y T11-26</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
@@ -17181,7 +18329,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H78" s="9" t="inlineStr"/>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 7 y 15</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
@@ -17215,7 +18367,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H79" s="9" t="inlineStr"/>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 7 · T-11 ítem T11-27</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
@@ -17249,7 +18405,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H80" s="9" t="inlineStr"/>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 7 · T-11 ítem T11-28</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
@@ -17351,7 +18511,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H83" s="9" t="inlineStr"/>
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 7</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
@@ -17385,7 +18549,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H84" s="9" t="inlineStr"/>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE RESUELTO en Subdoc. 4.2 v1.1, ap. 7 y Anexo A, lámina B · T-11 ítems T11-27 y T11-28. PENDIENTE: la doble acometida depende del levantamiento eléctrico VAL-01</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
@@ -17419,7 +18587,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H85" s="9" t="inlineStr"/>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 7 · T-11 ítem T11-29</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
@@ -17453,7 +18625,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H86" s="9" t="inlineStr"/>
+      <c r="H86" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 7 · T-11 ítems T11-29 y T11-13</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
@@ -17487,7 +18663,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H87" s="9" t="inlineStr"/>
+      <c r="H87" s="9" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE RESUELTO en Subdoc. 4.2 v1.1, ap. 7. PENDIENTE: el efecto en la eficiencia energética se cuantifica con el cálculo térmico de VAL-01</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
@@ -17521,7 +18701,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H88" s="9" t="inlineStr"/>
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 7 · T-11 ítem T11-30</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
@@ -17555,7 +18739,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H89" s="9" t="inlineStr"/>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 7 · T-11 ítem T11-30</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
@@ -17589,7 +18777,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H90" s="9" t="inlineStr"/>
+      <c r="H90" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 7 · T-11 ítem T11-30</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
@@ -17623,7 +18815,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H91" s="9" t="inlineStr"/>
+      <c r="H91" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 7 · T-11 ítem T11-30</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
@@ -17659,7 +18855,7 @@
       </c>
       <c r="H92" s="9" t="inlineStr">
         <is>
-          <t>La decisión lógica queda declarada en Subdoc. 4.1 v3.0, ap. 11.9; el detalle propio de este entregable se mantiene aquí.</t>
+          <t>La decisión lógica queda declarada en Subdoc. 4.1 v4.2, ap. 13.8; el detalle propio de este entregable se mantiene aquí.</t>
         </is>
       </c>
     </row>
@@ -17695,7 +18891,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H93" s="9" t="inlineStr"/>
+      <c r="H93" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 7 · T-11 ítem T11-31</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
@@ -17729,7 +18929,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H94" s="9" t="inlineStr"/>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 7 · T-11 ítem T11-31</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
@@ -17763,7 +18967,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H95" s="9" t="inlineStr"/>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 7 · T-11 ítem T11-31</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
@@ -17797,7 +19005,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H96" s="9" t="inlineStr"/>
+      <c r="H96" s="9" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE RESUELTO en Subdoc. 4.2 v1.1, ap. 7 · T-11 ítem T11-31. PENDIENTE: el respaldo en medio secundario de las grabaciones anteriores a 30 días se define con VAL-01</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
@@ -17831,7 +19043,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H97" s="9" t="inlineStr"/>
+      <c r="H97" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 7 y 14</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
@@ -17865,7 +19081,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H98" s="9" t="inlineStr"/>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 7 y 13 · T-11 ítem T11-19</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
@@ -17933,7 +19153,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H100" s="9" t="inlineStr"/>
+      <c r="H100" s="9" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE RESUELTO en Subdoc. 4.2 v1.1, ap. 7 y 13. PENDIENTE: la rotación y la verificación periódica de legibilidad se desarrollan en el Subdoc. 10</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
@@ -17967,7 +19191,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H101" s="9" t="inlineStr"/>
+      <c r="H101" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 7 y 8 · T-11 ítem T11-32</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
@@ -18001,7 +19229,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H102" s="9" t="inlineStr"/>
+      <c r="H102" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 7 · Anexo A, contenedor K4</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
@@ -18069,7 +19301,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H104" s="9" t="inlineStr"/>
+      <c r="H104" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 7 y 16, VAL-06 · T-11 ítems T11-23 y T11-24</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
@@ -18103,7 +19339,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H105" s="9" t="inlineStr"/>
+      <c r="H105" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 7 y 15</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
@@ -18137,7 +19377,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H106" s="9" t="inlineStr"/>
+      <c r="H106" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 6 · T-11, hojas «Cómo usarlo» y «Fichas técnicas»</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
@@ -18171,7 +19415,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H107" s="9" t="inlineStr"/>
+      <c r="H107" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 8</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
@@ -18205,7 +19453,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H108" s="9" t="inlineStr"/>
+      <c r="H108" s="9" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE RESUELTO en Subdoc. 4.2 v1.1, ap. 8. PENDIENTE: el análisis formal de amenazas comunes a ambos sitios se cierra con VAL-01</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
@@ -18239,7 +19491,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H109" s="9" t="inlineStr"/>
+      <c r="H109" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 8 y 12 · T-11 ítems T11-05 y T11-06</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
@@ -18273,7 +19529,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H110" s="9" t="inlineStr"/>
+      <c r="H110" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 8</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
@@ -18307,7 +19567,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H111" s="9" t="inlineStr"/>
+      <c r="H111" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 8 y 17</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
@@ -18341,7 +19605,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H112" s="9" t="inlineStr"/>
+      <c r="H112" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 8</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
@@ -18377,7 +19645,7 @@
       </c>
       <c r="H113" s="9" t="inlineStr">
         <is>
-          <t>Corrección de transcripción: RT-07.08 es «Se valorará que la conmutación sea automática…» y su carácter es Deseable, no Obligatorio. El error provenía del OCR y se corrigió al verificar la página 17 del PDF.</t>
+          <t>Corrección de transcripción: RT-07.08 es «Se valorará que la conmutación sea automática…» y su carácter es Deseable, no Obligatorio. El error provenía del OCR y se corrigió al verificar la página 17 del PDF. · PARCIALMENTE RESUELTO en Subdoc. 4.2 v1.1, ap. 8. La conmutación automática no se ofrece por decisión de diseño: el disparo lo declara el jefe de incidente, precisamente para evitar la conmutación innecesaria y el split-brain que el propio requisito manda proteger</t>
         </is>
       </c>
     </row>
@@ -18413,7 +19681,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H114" s="9" t="inlineStr"/>
+      <c r="H114" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 13 · T-11 ítem T11-19</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
@@ -18447,7 +19719,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H115" s="9" t="inlineStr"/>
+      <c r="H115" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 13 · T-11 ítem T11-12</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
@@ -18481,7 +19757,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H116" s="9" t="inlineStr"/>
+      <c r="H116" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 13 · T-11 ítems T11-08 y T11-19</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
@@ -18515,7 +19795,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H117" s="9" t="inlineStr"/>
+      <c r="H117" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 13</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
@@ -18549,7 +19833,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H118" s="9" t="inlineStr"/>
+      <c r="H118" s="9" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE RESUELTO en Subdoc. 5 v2.1, ap. 6.2 · Subdoc. 4.2 v1.1, ap. 13. PENDIENTE: la frecuencia de respaldo y el tiempo estimado de restauración completa por dominio se cierran con VAL-05</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
@@ -18617,7 +19905,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H120" s="9" t="inlineStr"/>
+      <c r="H120" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en T-11 ítems T11-15 a T11-19 y hoja «Dimensionamiento» · Subdoc. 4.2 v1.1, ap. 7, 8 y 12</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
@@ -18651,7 +19943,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H121" s="9" t="inlineStr"/>
+      <c r="H121" s="9" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE RESUELTO en T-11 ítems T11-17, T11-18 y T11-33 · Subdoc. 4.2 v1.1, ap. 7, 9 y 13. PENDIENTE: el monitoreo predictivo de salud de los medios se declara en el Subdoc. 10</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
@@ -18685,7 +19981,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H122" s="9" t="inlineStr"/>
+      <c r="H122" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en T-11 ítems T11-20 a T11-22 · Subdoc. 4.2 v1.1, ap. 4 y 13</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
@@ -18719,7 +20019,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H123" s="9" t="inlineStr"/>
+      <c r="H123" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en T-11 ítems T11-15, T11-16 y T11-27 · Subdoc. 4.2 v1.1, ap. 7</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="8" t="inlineStr">
@@ -18753,7 +20057,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H124" s="9" t="inlineStr"/>
+      <c r="H124" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en T-11, hoja «Fichas técnicas» · Subdoc. 4.2 v1.1, ap. 15</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
@@ -18787,7 +20095,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H125" s="9" t="inlineStr"/>
+      <c r="H125" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en T-11 ítem T11-32 · Subdoc. 4.2 v1.1, ap. 7 y 8</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="8" t="inlineStr">
@@ -18855,7 +20167,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H127" s="9" t="inlineStr"/>
+      <c r="H127" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en T-11 ítem T11-32 · Subdoc. 4.2 v1.1, ap. 14</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="8" t="inlineStr">
@@ -18889,7 +20205,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H128" s="9" t="inlineStr"/>
+      <c r="H128" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en T-11 ítem T11-38 · Subdoc. 4.2 v1.1, ap. 9.1</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
@@ -18923,7 +20243,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H129" s="9" t="inlineStr"/>
+      <c r="H129" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en T-11 ítem T11-38 · Subdoc. 4.2 v1.1, ap. 9.1</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="8" t="inlineStr">
@@ -18957,7 +20281,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H130" s="9" t="inlineStr"/>
+      <c r="H130" s="9" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE RESUELTO en T-11, hoja «Fichas técnicas» · Subdoc. 4.2 v1.1, ap. 14. PENDIENTE: el plan de reposición a lo largo de los 56 meses se cuantifica en la Oferta Económica</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
@@ -19025,7 +20353,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H132" s="9" t="inlineStr"/>
+      <c r="H132" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 14</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
@@ -19059,7 +20391,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H133" s="9" t="inlineStr"/>
+      <c r="H133" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 14 · Subdoc. 5 v2.1, ap. 6.4</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="8" t="inlineStr">
@@ -19093,7 +20429,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H134" s="9" t="inlineStr"/>
+      <c r="H134" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 14</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
@@ -19153,7 +20493,7 @@
       <c r="E136" s="9" t="inlineStr"/>
       <c r="F136" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G136" s="9" t="inlineStr">
@@ -19163,7 +20503,7 @@
       </c>
       <c r="H136" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 10 y 13.1</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 12.2</t>
         </is>
       </c>
     </row>
@@ -19201,7 +20541,7 @@
       </c>
       <c r="H137" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -19239,7 +20579,7 @@
       </c>
       <c r="H138" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -19267,7 +20607,7 @@
       <c r="E139" s="9" t="inlineStr"/>
       <c r="F139" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G139" s="9" t="inlineStr">
@@ -19277,7 +20617,7 @@
       </c>
       <c r="H139" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 13.2</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 12.3</t>
         </is>
       </c>
     </row>
@@ -19315,7 +20655,7 @@
       </c>
       <c r="H140" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -19353,7 +20693,7 @@
       </c>
       <c r="H141" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -19525,7 +20865,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H146" s="9" t="inlineStr"/>
+      <c r="H146" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 4.2 v1.1, ap. 8</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
@@ -19559,7 +20903,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H147" s="9" t="inlineStr"/>
+      <c r="H147" s="9" t="inlineStr">
+        <is>
+          <t>RESUELTO en Subdoc. 5 v2.1, ap. 4.5 · Subdoc. 4.2 v1.1, ap. 11</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="8" t="inlineStr">
@@ -19619,7 +20967,7 @@
       <c r="E149" s="9" t="inlineStr"/>
       <c r="F149" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G149" s="9" t="inlineStr">
@@ -19629,7 +20977,7 @@
       </c>
       <c r="H149" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 11.1</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 13.1</t>
         </is>
       </c>
     </row>
@@ -19657,7 +21005,7 @@
       <c r="E150" s="9" t="inlineStr"/>
       <c r="F150" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G150" s="9" t="inlineStr">
@@ -19667,7 +21015,7 @@
       </c>
       <c r="H150" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 11.2</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 13.5</t>
         </is>
       </c>
     </row>
@@ -19695,7 +21043,7 @@
       <c r="E151" s="9" t="inlineStr"/>
       <c r="F151" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G151" s="9" t="inlineStr">
@@ -19705,7 +21053,7 @@
       </c>
       <c r="H151" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 11.3</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 13.2</t>
         </is>
       </c>
     </row>
@@ -19743,7 +21091,7 @@
       </c>
       <c r="H152" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -19781,7 +21129,7 @@
       </c>
       <c r="H153" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -19819,7 +21167,7 @@
       </c>
       <c r="H154" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -19847,7 +21195,7 @@
       <c r="E155" s="9" t="inlineStr"/>
       <c r="F155" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G155" s="9" t="inlineStr">
@@ -19857,7 +21205,7 @@
       </c>
       <c r="H155" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 11.4</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 13.3</t>
         </is>
       </c>
     </row>
@@ -19885,7 +21233,7 @@
       <c r="E156" s="9" t="inlineStr"/>
       <c r="F156" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G156" s="9" t="inlineStr">
@@ -19895,7 +21243,7 @@
       </c>
       <c r="H156" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 11.5</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 13.4</t>
         </is>
       </c>
     </row>
@@ -19923,7 +21271,7 @@
       <c r="E157" s="9" t="inlineStr"/>
       <c r="F157" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G157" s="9" t="inlineStr">
@@ -19933,7 +21281,7 @@
       </c>
       <c r="H157" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 11.5</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 13.4</t>
         </is>
       </c>
     </row>
@@ -19961,7 +21309,7 @@
       <c r="E158" s="9" t="inlineStr"/>
       <c r="F158" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G158" s="9" t="inlineStr">
@@ -19971,7 +21319,7 @@
       </c>
       <c r="H158" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 11.6</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 5, capa 3</t>
         </is>
       </c>
     </row>
@@ -19999,7 +21347,7 @@
       <c r="E159" s="9" t="inlineStr"/>
       <c r="F159" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G159" s="9" t="inlineStr">
@@ -20009,7 +21357,7 @@
       </c>
       <c r="H159" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 11.4</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 13.3</t>
         </is>
       </c>
     </row>
@@ -20037,7 +21385,7 @@
       <c r="E160" s="9" t="inlineStr"/>
       <c r="F160" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G160" s="9" t="inlineStr">
@@ -20047,7 +21395,7 @@
       </c>
       <c r="H160" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 11.4, con la enumeración concreta en el Subdoc. 4.2</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 13.3. La enumeracion concreta de dominios, puertos y servicios es del Subdoc. 4.2.</t>
         </is>
       </c>
     </row>
@@ -20075,7 +21423,7 @@
       <c r="E161" s="9" t="inlineStr"/>
       <c r="F161" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G161" s="9" t="inlineStr">
@@ -20085,7 +21433,7 @@
       </c>
       <c r="H161" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 11.7</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 14.5</t>
         </is>
       </c>
     </row>
@@ -20113,7 +21461,7 @@
       <c r="E162" s="9" t="inlineStr"/>
       <c r="F162" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G162" s="9" t="inlineStr">
@@ -20123,7 +21471,7 @@
       </c>
       <c r="H162" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 11.7</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 13.6</t>
         </is>
       </c>
     </row>
@@ -20161,7 +21509,7 @@
       </c>
       <c r="H163" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -20199,7 +21547,7 @@
       </c>
       <c r="H164" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -20237,7 +21585,7 @@
       </c>
       <c r="H165" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -20275,7 +21623,7 @@
       </c>
       <c r="H166" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -20313,7 +21661,7 @@
       </c>
       <c r="H167" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -20351,7 +21699,7 @@
       </c>
       <c r="H168" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -20389,7 +21737,7 @@
       </c>
       <c r="H169" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -20427,7 +21775,7 @@
       </c>
       <c r="H170" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -20455,7 +21803,7 @@
       <c r="E171" s="9" t="inlineStr"/>
       <c r="F171" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G171" s="9" t="inlineStr">
@@ -20465,7 +21813,7 @@
       </c>
       <c r="H171" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 11.8</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 13.7</t>
         </is>
       </c>
     </row>
@@ -20503,7 +21851,7 @@
       </c>
       <c r="H172" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -20531,7 +21879,7 @@
       <c r="E173" s="9" t="inlineStr"/>
       <c r="F173" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G173" s="9" t="inlineStr">
@@ -20541,7 +21889,7 @@
       </c>
       <c r="H173" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 11.8</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 13.7</t>
         </is>
       </c>
     </row>
@@ -20579,7 +21927,7 @@
       </c>
       <c r="H174" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -20607,7 +21955,7 @@
       <c r="E175" s="9" t="inlineStr"/>
       <c r="F175" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G175" s="9" t="inlineStr">
@@ -20617,7 +21965,7 @@
       </c>
       <c r="H175" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 11.9</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 13.8</t>
         </is>
       </c>
     </row>
@@ -20645,7 +21993,7 @@
       <c r="E176" s="9" t="inlineStr"/>
       <c r="F176" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G176" s="9" t="inlineStr">
@@ -20655,7 +22003,7 @@
       </c>
       <c r="H176" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 16.5</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 16.5</t>
         </is>
       </c>
     </row>
@@ -20683,7 +22031,7 @@
       <c r="E177" s="9" t="inlineStr"/>
       <c r="F177" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G177" s="9" t="inlineStr">
@@ -20693,7 +22041,7 @@
       </c>
       <c r="H177" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 4 capa 8 y 12.1</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 5 capa 8, y 14.1</t>
         </is>
       </c>
     </row>
@@ -20721,7 +22069,7 @@
       <c r="E178" s="9" t="inlineStr"/>
       <c r="F178" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G178" s="9" t="inlineStr">
@@ -20731,7 +22079,7 @@
       </c>
       <c r="H178" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 12.5</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 14.5</t>
         </is>
       </c>
     </row>
@@ -20759,7 +22107,7 @@
       <c r="E179" s="9" t="inlineStr"/>
       <c r="F179" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G179" s="9" t="inlineStr">
@@ -20769,7 +22117,7 @@
       </c>
       <c r="H179" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 12.2</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 14.2</t>
         </is>
       </c>
     </row>
@@ -20797,7 +22145,7 @@
       <c r="E180" s="9" t="inlineStr"/>
       <c r="F180" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G180" s="9" t="inlineStr">
@@ -20807,7 +22155,7 @@
       </c>
       <c r="H180" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 12.3</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 14.3</t>
         </is>
       </c>
     </row>
@@ -20845,7 +22193,7 @@
       </c>
       <c r="H181" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -20883,7 +22231,7 @@
       </c>
       <c r="H182" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -20911,7 +22259,7 @@
       <c r="E183" s="9" t="inlineStr"/>
       <c r="F183" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G183" s="9" t="inlineStr">
@@ -20921,7 +22269,7 @@
       </c>
       <c r="H183" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 12.4</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 14.4</t>
         </is>
       </c>
     </row>
@@ -20949,7 +22297,7 @@
       <c r="E184" s="9" t="inlineStr"/>
       <c r="F184" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G184" s="9" t="inlineStr">
@@ -20959,7 +22307,7 @@
       </c>
       <c r="H184" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 12.6</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 14.5</t>
         </is>
       </c>
     </row>
@@ -20987,7 +22335,7 @@
       <c r="E185" s="9" t="inlineStr"/>
       <c r="F185" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G185" s="9" t="inlineStr">
@@ -20997,7 +22345,7 @@
       </c>
       <c r="H185" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 12.7</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 14.6</t>
         </is>
       </c>
     </row>
@@ -21033,7 +22381,11 @@
           <t>Grupo 3 / sin asignar</t>
         </is>
       </c>
-      <c r="H186" s="9" t="inlineStr"/>
+      <c r="H186" s="9" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE RESUELTO en Subdoc. 4.2 v1.1, ap. 12 y 16, VAL-05, con gatillo de expansión al 70 % sostenido. PENDIENTE: el factor de utilización proyectado se declara con el perfil de carga real de VAL-05</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="8" t="inlineStr">
@@ -21063,7 +22415,7 @@
       </c>
       <c r="F187" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G187" s="9" t="inlineStr">
@@ -21073,7 +22425,7 @@
       </c>
       <c r="H187" s="9" t="inlineStr">
         <is>
-          <t>El caso usa RT-15.02 para las certificaciones sectoriales del adjudicatario. El RT-15.02 transversal es el apagado de ambientes no productivos; las certificaciones están en el numeral 15.2 (RT-15.07 a RT-15.09). · RESUELTO en Subdoc. 4.1 v3.0, ap. 16.6</t>
+          <t>El caso usa RT-15.02 para las certificaciones sectoriales del adjudicatario. El RT-15.02 transversal es el apagado de ambientes no productivos; las certificaciones están en el numeral 15.2 (RT-15.07 a RT-15.09). · RESUELTO en Subdoc. 4.1 v4.2, ap. 15.8</t>
         </is>
       </c>
     </row>
@@ -21143,7 +22495,11 @@
           <t>Grupo 3 / sin asignar</t>
         </is>
       </c>
-      <c r="H189" s="9" t="inlineStr"/>
+      <c r="H189" s="9" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE RESUELTO en Subdoc. 4.2 v1.1, ap. 7. PENDIENTE: la intensidad de carbono de Azure Chile Central se declara con el dato publicado del proveedor</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="8" t="inlineStr">
@@ -21339,7 +22695,7 @@
       <c r="E195" s="9" t="inlineStr"/>
       <c r="F195" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G195" s="9" t="inlineStr">
@@ -21349,7 +22705,7 @@
       </c>
       <c r="H195" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 13.4</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 15.2</t>
         </is>
       </c>
     </row>
@@ -21387,7 +22743,7 @@
       </c>
       <c r="H196" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -21415,7 +22771,7 @@
       <c r="E197" s="9" t="inlineStr"/>
       <c r="F197" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G197" s="9" t="inlineStr">
@@ -21425,7 +22781,7 @@
       </c>
       <c r="H197" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 16.7</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 16.6</t>
         </is>
       </c>
     </row>
@@ -21463,7 +22819,7 @@
       </c>
       <c r="H198" s="9" t="inlineStr">
         <is>
-          <t>Reasignado desde «Subdoc. 4.1» por el apartado 15 del Subdoc. 4.1 v3.0: no es materia de arquitectura lógica.</t>
+          <t>Reasignado desde «Subdoc. 4.1» por el apartado 19 del Subdoc. 4.1 v4.2: no es materia de arquitectura lógica.</t>
         </is>
       </c>
     </row>
@@ -21491,7 +22847,7 @@
       <c r="E199" s="9" t="inlineStr"/>
       <c r="F199" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G199" s="9" t="inlineStr">
@@ -21501,7 +22857,7 @@
       </c>
       <c r="H199" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 16.2 y 16.3</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 16.2 y 16.3</t>
         </is>
       </c>
     </row>
@@ -21529,7 +22885,7 @@
       <c r="E200" s="9" t="inlineStr"/>
       <c r="F200" s="9" t="inlineStr">
         <is>
-          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v3.0)</t>
+          <t>Subdoc. 4.1 — Arquitectura lógica (entregado v4.2)</t>
         </is>
       </c>
       <c r="G200" s="9" t="inlineStr">
@@ -21539,7 +22895,7 @@
       </c>
       <c r="H200" s="9" t="inlineStr">
         <is>
-          <t>RESUELTO en Subdoc. 4.1 v3.0, ap. 16.4</t>
+          <t>RESUELTO en Subdoc. 4.1 v4.2, ap. 16.4</t>
         </is>
       </c>
     </row>
@@ -23487,7 +24843,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H257" s="9" t="inlineStr"/>
+      <c r="H257" s="9" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE RESUELTO en Subdoc. 1 v1.0, ap. 2 y 6. PENDIENTE: el sitio corporativo es simulado para el ejercicio académico (dominio .example) y no está activo; el contenido exigido está íntegro en el subdocumento</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="8" t="inlineStr">
@@ -23521,7 +24881,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H258" s="9" t="inlineStr"/>
+      <c r="H258" s="9" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE RESUELTO en Subdoc. 1 v1.0, ap. 8 y 9 · Formulario T-6 v1.0. PENDIENTE: publicación en sitio activo; los tres proyectos son simulados y están rotulados como tales</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="8" t="inlineStr">
@@ -23555,7 +24919,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H259" s="9" t="inlineStr"/>
+      <c r="H259" s="9" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE RESUELTO en Subdoc. 1 v1.0, ap. 5, 5.1 y 6. PENDIENTE: publicación en sitio activo; la asignación nominal y la evidencia de certificaciones corresponden al Formulario T-8</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="8" t="inlineStr">
@@ -23589,7 +24957,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="H260" s="9" t="inlineStr"/>
+      <c r="H260" s="9" t="inlineStr">
+        <is>
+          <t>PARCIALMENTE RESUELTO en Subdoc. 1 v1.0, ap. 3, 4 y 7. PENDIENTE: publicación en sitio activo</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="8" t="inlineStr">
